--- a/results/Int Task Remove ACC 0.8/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.8/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.0011296660117878332 +/- 0.0006232110776252297</t>
+          <t>0.008693516699410597 +/- 0.0012435156091524786</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,379 +886,379 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.0009823182711198642 +/- 0.0007285067276125317</t>
+          <t>0.009037328094302566 +/- 0.001571709233791766</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.00024557956777992995 +/- 0.0005914339184082564</t>
+          <t>0.004322200392927311 +/- 0.0009003095667889858</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.0001473477406680024 +/- 0.0006963382553417374</t>
+          <t>0.0027504911591355596 +/- 0.0010805500982318148</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.0025540275049116268 +/- 0.0009003095667889605</t>
+          <t>0.004469548133595291 +/- 0.0009175609868501646</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.00014734774066801348 +/- 0.00100777428922805</t>
+          <t>0.0017681728880157288 +/- 0.0014767481707635406</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0003438113948919574 +/- 0.00044204322200394174</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.008693516699410587 +/- 0.0010314341846758264</t>
+          <t>0.008055009823182713 +/- 0.0012464221552504393</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.0015225933202357989 +/- 0.001830515241020055</t>
+          <t>-0.002259332023575633 +/- 0.002131879608468611</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.00427308447937128 +/- 0.0020375705808144853</t>
+          <t>9.823182711198309e-05 +/- 0.002394117408045959</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.0023575638506876384 +/- 0.0010255703839794489</t>
+          <t>-0.00520628683693517 +/- 0.0011869396830643101</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-0.001866404715127712 +/- 0.0008450221283931725</t>
+          <t>0.006581532416502944 +/- 0.0013397035065801396</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.001326129666011755 +/- 0.0009332023575638601</t>
+          <t>0.0036836935166994155 +/- 0.0013584790457700823</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.012229862475442077 +/- 0.0015130571513506416</t>
+          <t>-0.013015717092337908 +/- 0.0020280768980415094</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.0031434184675835364 +/- 0.0015717092337917682</t>
+          <t>0.0008349705304518618 +/- 0.002495262435339974</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.0006385068762278734 +/- 0.0010771960805236339</t>
+          <t>0.011493123772102154 +/- 0.001718355175298224</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.0004911591355599376 +/- 0.0007919703092631023</t>
+          <t>0.009184675834970523 +/- 0.0012239622587796792</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-0.003929273084479412 +/- 0.0012030892646282744</t>
+          <t>-0.001915520628683698 +/- 0.0009933078789860876</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.00417485265225932 +/- 0.0008291720538376109</t>
+          <t>0.00677799607072691 +/- 0.0007858546168958743</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>9.823182711197199e-05 +/- 0.000196463654223944</t>
+          <t>-0.00014734774066798017 +/- 0.00038360754793256136</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.005009823182711237 +/- 0.0014201210505698299</t>
+          <t>-0.007465618860510814 +/- 0.001238656209520497</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0006385068762278622 +/- 0.0007624840224096168</t>
+          <t>-0.0009823182711198419 +/- 0.0007609004609444878</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.00103143418467585 +/- 0.0006385068762278837</t>
+          <t>-0.0006385068762279067 +/- 0.0009587043858518381</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.002013752455795703 +/- 0.0005127851919897176</t>
+          <t>0.00029469548133594927 +/- 0.0009872176445108974</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.002455795677799644 +/- 0.0011622946528683218</t>
+          <t>-0.0028978388998035175 +/- 0.0007432586419656909</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.000491159135559871 +/- 0.00021965304297640102</t>
+          <t>-0.00230844793713163 +/- 0.0005402750491158943</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.0030943025540275393 +/- 0.0008521292521069352</t>
+          <t>-0.005255402750491145 +/- 0.0012627662212359994</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.0011787819253437637 +/- 0.0005469316662897714</t>
+          <t>0.004911591355599221 +/- 0.00109826521488202</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-0.00029469548133598256 +/- 0.0006662406663187903</t>
+          <t>0.0051080550098231755 +/- 0.001145570116865491</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.0007609004609444662</t>
+          <t>0.0016699410609037567 +/- 0.0007672150958650873</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>-4.911591355599709e-05 +/- 0.000264497289152016</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-0.00029469548133594927 +/- 0.0006289905930680781</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.0024066797642436134 +/- 0.0013078120781625155</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-0.0006876227897838927 +/- 0.0010579891566079684</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.0005402750491159347 +/- 0.0004633586017709562</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.0012278978388998163 +/- 0.0005914339184082426</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>-0.002259332023575633 +/- 0.0010349365179619502</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.0012770137524557913 +/- 0.0011664383189624783</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-0.00019646365422396617 +/- 0.0006289905930680608</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.0007858546168958757 +/- 0.0010579891566079571</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-9.823182711197199e-05 +/- 0.0004812357058513197</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.00103143418467585 +/- 0.0004633586017709621</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.0035363457760314134 +/- 0.0011156990856189281</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>-0.012278978388998042 +/- 0.001824575208350363</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.00034381139489193525 +/- 0.0010771960805236512</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>-0.0006385068762279178 +/- 0.0006963382553417413</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.000834970530451884 +/- 0.0003144952965340131</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>-0.006434184675834964 +/- 0.001464445139084028</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.0016208251473477375 +/- 0.0014073230630544528</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.002210216110019636 +/- 0.0014107472118217329</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.010363457760314342 +/- 0.0018952633970112588</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-9.823182711199419e-05 +/- 0.0003675498415298938</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.00024557956777997435 +/- 0.0003959851546315787</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.00029469548133596033 +/- 0.0005008860032999006</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.007662082514734769 +/- 0.001917408771703665</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.00024557956777996324 +/- 0.0007995491451915568</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.00034381139489194636 +/- 0.0006963382553417482</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>-0.0024066797642436134 +/- 0.0006385068762278836</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.0005893909626719096 +/- 0.0012386562095204954</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>9.823182711199419e-05 +/- 0.00042818260742054153</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-0.0013261296660118105 +/- 0.0010077742892280479</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.002210216110019647 +/- 0.0013761223699530274</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-0.007563850687622786 +/- 0.00112431465051665</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>0.00044204322200392944 +/- 0.0007432586419657013</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>-0.0008840864440078477 +/- 0.0009003095667889677</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>9.823182711198309e-05 +/- 0.00042818260742051866</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0.0005402750491159236 +/- 0.0008349705304518683</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0.0011787819253438413 +/- 0.0006662406663187756</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>-0.002259332023575633 +/- 0.0009370719070893307</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>-0.0007367387033399009 +/- 0.0010361013315191125</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>-9.823182711199419e-05 +/- 0.00019646365422398837</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.0006385068762279067 +/- 0.0009332023575638601</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
           <t>-4.911591355599709e-05 +/- 0.00014734774066799128</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.00019646365422394397 +/- 0.0003929273084479295</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-0.000834970530451884 +/- 0.0008233327413673956</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>-0.00019646365422398837 +/- 0.00024061785292568027</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.0005402750491159015 +/- 0.000463358601770948</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>-0.0007367387033399009 +/- 0.0009122876041751636</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>-0.0007367387033399009 +/- 0.0005032883480333594</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-0.00039292730844797674 +/- 0.0003675498415298493</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.0011296660117878221 +/- 0.0011424070088028356</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.000933202357563856 +/- 0.00026449728915197893</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>-3.3306690738754695e-17 +/- 0.0004911591355599265</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.0014734774066797241 +/- 0.0003804502304722367</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>-0.013163064833005934 +/- 0.0009003095667889593</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>-0.0017190569744597428 +/- 0.0009637238148501278</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>-0.002161100196463672 +/- 0.0005893909626719022</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>-9.823182711199419e-05 +/- 0.00019646365422398837</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>-0.0027013752455796068 +/- 0.0008577725538591971</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0006876227897838483 +/- 0.0005008860032998876</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-0.0005402750491159347 +/- 0.0009933078789860768</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.003045186640471498 +/- 0.0013142522750746416</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-0.0008840864440078589 +/- 0.00019646365422394395</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>-0.0003929273084479545 +/- 0.00048123570585129933</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>9.823182711198309e-05 +/- 0.00029469548133594927</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.0035363457760314134 +/- 0.0017817639633808577</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-0.000982318271119853 +/- 0.0006212726247874845</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>-4.911591355599709e-05 +/- 0.00014734774066799128</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>-3.3306690738754695e-17 +/- 0.0003804502304722367</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.00024557956777994107 +/- 0.000630905332940325</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>4.911591355598599e-05 +/- 0.00014734774066795797</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-0.0023084479371316634 +/- 0.0005402750491159337</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.0015717092337917294 +/- 0.0008159748391864682</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-0.005550098231827139 +/- 0.0014243614931237793</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>-0.00103143418467585 +/- 0.0005578495428094528</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>-0.0005402750491159347 +/- 0.0006385068762278793</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>-0.0006876227897839038 +/- 0.0005469316662897714</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>-0.0005893909626719318 +/- 0.0008159748391864374</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>-0.0005402750491159347 +/- 0.0006385068762278964</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>-0.00039292730844796563 +/- 0.0007545329811265703</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>-0.00034381139489196854 +/- 0.00044204322200392076</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>-0.00019646365422399948 +/- 0.0007672150958650829</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>-0.0005893909626719207 +/- 0.0004812357058513129</t>
-        </is>
-      </c>
       <c r="CA2" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-0.00024557956777998546 +/- 0.0002455795677799854</t>
+          <t>-0.0005402750491159236 +/- 0.0006385068762279144</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-0.00407662082514737 +/- 0.0007301605475107348</t>
+          <t>-0.0017190569744597317 +/- 0.0008577725538591717</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>-0.00029469548133596033 +/- 0.0003929273084479379</t>
+          <t>-0.00024557956777998546 +/- 0.00032947956446463875</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0015225933202357655 +/- 0.0007750360431266903</t>
+          <t>0.001080550098231836 +/- 0.0012957667935435165</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>-0.0021611001964636613 +/- 0.0003929273084479573</t>
+          <t>-0.0005893909626719096 +/- 0.0010938633325795726</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.0005402750491159347 +/- 0.0004633586017709562</t>
+          <t>-0.000933202357563856 +/- 0.0007750360431266968</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.0016208251473477486 +/- 0.00073016054751074</t>
+          <t>-0.003143418467583492 +/- 0.0004501547833944754</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-0.0024066797642436468 +/- 0.00046335860177097737</t>
+          <t>-0.0028487229862475317 +/- 0.0008159748391864507</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>-0.0004420432220039516 +/- 0.00034381139489194474</t>
+          <t>-0.0006385068762279178 +/- 0.00044204322200392694</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.0038723181580324396 +/- 0.0010517923203684978</t>
+          <t>1.1102230246251566e-17 +/- 0.0005232862375719405</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,27 +1331,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.007639979068550473 +/- 0.0014080192618601513</t>
+          <t>-0.004604918890633169 +/- 0.0016679620565681992</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.004918890633176331 +/- 0.0011271930522521107</t>
+          <t>-0.0024071166928309575 +/- 0.0005336493473147827</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.003924646781789653 +/- 0.0011284070461982062</t>
+          <t>-0.00031397174254315096 +/- 0.0009419152276295146</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.00026164311878595914 +/- 0.00026164311878595914</t>
+          <t>0.001883830455259039 +/- 0.0013685710968730702</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.004133961276818421 +/- 0.0011088236577926256</t>
+          <t>-0.0032967032967032963 +/- 0.0006639758001281926</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1361,127 +1361,127 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0021454735740450205 +/- 0.0006387522561870078</t>
+          <t>-0.003715332286760831 +/- 0.001032081785626156</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.011407639979068573 +/- 0.0018838304552590095</t>
+          <t>0.010779696493982227 +/- 0.0016580826287550916</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.016064887493458947 +/- 0.00299738429965875</t>
+          <t>0.01156462585034016 +/- 0.0019919274003845438</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.0058608058608058625 +/- 0.0012114952279215353</t>
+          <t>0.0014128728414442792 +/- 0.0008771875779298853</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.00041862899005759016 +/- 0.0007326007326007331</t>
+          <t>0.0003139717425431843 +/- 0.0007098199877682092</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0023547880690737875 +/- 0.0011759395632781097</t>
+          <t>0.0006802721088435381 +/- 0.0007040096309300764</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.02030350601779176 +/- 0.002167693896097109</t>
+          <t>0.009680795395081121 +/- 0.002083310228926663</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.025117739403453708 +/- 0.0020131223507767037</t>
+          <t>0.006698063840920998 +/- 0.001926944284617687</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-0.007430664573521683 +/- 0.0012114952279215344</t>
+          <t>-0.004186289900575624 +/- 0.0013645635594354156</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.0036630036630036834 +/- 0.00066191055157894</t>
+          <t>-0.002040816326530581 +/- 0.00145111717675166</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.007116692830978521 +/- 0.0009705513862371295</t>
+          <t>0.0002616431187859924 +/- 0.0021094342617212253</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.0023547880690737654 +/- 0.0014661356071294358</t>
+          <t>-0.00015698587127157548 +/- 0.0005756148613291101</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00010465724751438366 +/- 0.00020931449502876732</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.000784929356357944 +/- 0.0014089913153151588</t>
+          <t>-0.0015698587127158325 +/- 0.0005232862375719626</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.0033490319204605213 +/- 0.0010775123119819178</t>
+          <t>0.002302459445316596 +/- 0.0008818576424046347</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-0.006959706959706924 +/- 0.0010478798741235355</t>
+          <t>-0.0021978021978021787 +/- 0.00111743362135334</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.0015175300889586519 +/- 0.0011332500171485022</t>
+          <t>-0.0019884877027734004 +/- 0.0008372579801151316</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.004133961276818398 +/- 0.0005943389163579495</t>
+          <t>-0.0018838304552590058 +/- 0.0007098199877682207</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0005756148613291434 +/- 0.0004936672491918802</t>
+          <t>-0.0007326007326007078 +/- 0.00047959975876043083</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.0023547880690737875 +/- 0.0009997369531419627</t>
+          <t>-0.002511773940345341 +/- 0.0007690705628832725</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.0037676609105180446 +/- 0.001763715284809296</t>
+          <t>0.0010465724751439031 +/- 0.0007400384941774669</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.003349031920460499 +/- 0.001151229722658301</t>
+          <t>0.0007326007326007522 +/- 0.0011026325225382259</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0014128728414442792 +/- 0.0011944230466261934</t>
+          <t>-0.0017268445839874191 +/- 0.001704499997373342</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5.232862375721403e-05 +/- 0.0005463268712145815</t>
+          <t>-0.0005232862375719183 +/- 0.00023402071978018273</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.0009419152276294862 +/- 0.0005635965261260713</t>
+          <t>0.0002616431187859924 +/- 0.0005850517994505016</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.0031397174254317204 +/- 0.0014426006019979262</t>
+          <t>-0.0032967032967032737 +/- 0.0008123586968215507</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.232862375719183e-05 +/- 0.001432122677488635</t>
+          <t>0.003767660910518067 +/- 0.0009873344983837168</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1506,257 +1506,257 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.00020931449502876732 +/- 0.0003471088215965659</t>
+          <t>5.232862375720293e-05 +/- 0.0005943389163579368</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.0009942438513867113 +/- 0.0010320817856261475</t>
+          <t>-0.00293040293040292 +/- 0.0016580826287551015</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.001151229722658309 +/- 0.0010926537424291428</t>
+          <t>-0.00010465724751438366 +/- 0.000512713708588806</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.00036630036630034277 +/- 0.0004086996167402487</t>
+          <t>0.0001569858712715866 +/- 0.0010736935912445253</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.002721088435374175 +/- 0.0005127137085888445</t>
+          <t>-0.0014652014652014266 +/- 0.0016842989994171641</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.005075876504447918 +/- 0.0007418862835561263</t>
+          <t>0.0017268445839874413 +/- 0.001047879874123536</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0013082155939298846 +/- 0.0007849293563579366</t>
+          <t>-0.0027210884353741195 +/- 0.0014002185411051515</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-0.0007849293563579219 +/- 0.00132898221864995</t>
+          <t>0.0035060177917320967 +/- 0.0007418862835561514</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>-0.006488749345892187 +/- 0.0012860497883249108</t>
+          <t>0.003767660910518067 +/- 0.0015663662529665835</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.005389848246991092 +/- 0.0017044999973733431</t>
+          <t>-0.006227106227106216 +/- 0.0018493560488824902</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.01145996860282572 +/- 0.0020327498272689807</t>
+          <t>-0.008948194662480369 +/- 0.0010320817856261718</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>-0.00047095761381472646 +/- 0.00015698587127157548</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>-0.0077969649398220596 +/- 0.001226098850220828</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>-0.00586080586080584 +/- 0.0014387992762812552</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.00680272108843537 +/- 0.0008756253548237484</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.0007326007326007522 +/- 0.0016077751434576022</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-0.0007326007326006967 +/- 0.0004186289900575568</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>-0.0006279434850863019 +/- 0.00039159156324162234</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>-0.0014652014652014379 +/- 0.00039159156324166983</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.005337519623233922 +/- 0.001298762286341263</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-0.0015698587127158325 +/- 0.0011464627054006693</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-0.00026164311878595914 +/- 0.00042188685234421935</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>-0.005023547880690727 +/- 0.001573343420028565</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>-0.0008372579801151026 +/- 0.0012645783331862292</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>-0.0005756148613291101 +/- 0.0003663003663003428</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>-0.008163265306122436 +/- 0.0014463919373192483</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-0.002197802197802168 +/- 0.0012114952279215488</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-0.002250130821559393 +/- 0.0017830167490738627</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-0.00031397174254315096 +/- 0.0003471088215965659</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>-0.0027210884353741083 +/- 0.0009873344983837356</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>-0.0005756148613291323 +/- 0.0007918757692528131</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>-0.001046572475143892 +/- 0.001072417662580807</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>-0.002511773940345352 +/- 0.0013196776779611028</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>-0.00010465724751436145 +/- 0.0007326007326007205</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>-0.0038199895342752367 +/- 0.0009375443677220907</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>-0.00010465724751438366 +/- 0.00020931449502876732</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>-0.0005756148613291101 +/- 0.00028179826306301195</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>-0.0015175300889586408 +/- 0.0007918757692528417</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>-0.00015698587127157548 +/- 0.00047095761381472646</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>-0.0004186289900575457 +/- 0.0007690705628832332</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
           <t>5.232862375719183e-05 +/- 0.00015698587127157548</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>-0.009837781266352675 +/- 0.0013402667163647868</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>-0.007378335949764503 +/- 0.0016289254229485434</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-0.0005232862375719293 +/- 0.0009063583503761718</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-0.002145473574044976 +/- 0.0019781327233318585</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-5.232862375719183e-05 +/- 0.00028179826306301195</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.0008372579801151359 +/- 0.0002563568542944574</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.0016221873364730577 +/- 0.0003663003663003428</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.006698063840920987 +/- 0.0013196776779611345</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-0.006907378335949743 +/- 0.0014387992762812545</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.0008895866038723166 +/- 0.0005258961601842593</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>-0.010204081632653027 +/- 0.0016423186631580593</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>-0.000261643118785948 +/- 0.0009433676806551434</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.0006802721088435271 +/- 0.0002397998793802469</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-0.013553113553113528 +/- 0.0017737782581557764</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.009733124018838324 +/- 0.0014463919373192316</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-0.002616431187859736 +/- 0.0008437737046885007</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.0012035583464154898 +/- 0.0005756148613291495</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>-0.0012035583464154675 +/- 0.0008771875779298774</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>-0.0028257456828885254 +/- 0.000970551386237108</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>-0.0016745159602302162 +/- 0.0006942176431931786</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>-0.003924646781789642 +/- 0.0011759395632780776</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.0006802721088435493 +/- 0.0007779209182270266</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>-0.0018838304552590058 +/- 0.0015733434200285738</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.000366300366300365 +/- 0.00040869961674028574</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>-0.0012035583464154564 +/- 0.00047095761381477335</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.0009419152276295307 +/- 0.0006102513757033309</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>-0.00015698587127157548 +/- 0.000239799879380196</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>-0.0029827315541601116 +/- 0.001481001747575619</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>-0.0010989010989010505 +/- 0.0005943389163579555</t>
+          <t>-0.00026164311878595914 +/- 0.0003510310796702741</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.00047095761381475975 +/- 0.000791875769252824</t>
+          <t>-0.0005756148613291212 +/- 0.0010052000372735895</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.0032967032967032963 +/- 0.000525896160184235</t>
+          <t>-0.0026164311878597466 +/- 0.0007400384941774435</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-0.0008895866038722833 +/- 0.0007040096309300583</t>
+          <t>-0.00104657247514387 +/- 0.0004053357766831585</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>-0.0004186289900575568 +/- 0.0008372579801150998</t>
+          <t>-0.0026687598116169275 +/- 0.0008582532426403416</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>-0.00580847723704866 +/- 0.0015776884805527125</t>
+          <t>-0.000261643118785948 +/- 0.0006721733426826121</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.00031397174254315096 +/- 0.0009419152276294899</t>
+          <t>-0.001831501831501814 +/- 0.0008518482781841983</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.009882478632478597 +/- 0.0013981038812288839</t>
+          <t>-0.0001602564102564097 +/- 0.0007573422477968897</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,122 +1776,122 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.005395299145299126 +/- 0.0010535834894933734</t>
+          <t>-0.0005341880341880323 +/- 0.0005341880341880323</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.005448717948717929 +/- 0.0006229649460304786</t>
+          <t>0.0010149572649572614 +/- 0.0008761335185286681</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.002777777777777768 +/- 0.0012367347118365582</t>
+          <t>0.0005341880341880323 +/- 0.0005341880341880323</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.02297008547008539 +/- 0.0015665468267751206</t>
+          <t>-0.0006410256410256387 +/- 0.000820635229473139</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.006517094017093994 +/- 0.001651669319844044</t>
+          <t>-0.00042735042735042583 +/- 0.0006229649460304786</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-5.341880341880323e-05 +/- 0.0001602564102564097</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.003258547008547108 +/- 0.001131924150663302</t>
+          <t>0.005502136752136733 +/- 0.0011217948717948676</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0363782051282052 +/- 0.004000708193024111</t>
+          <t>0.0020299145299145227 +/- 0.0020799062322576617</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.013995726495726557 +/- 0.004094822200157422</t>
+          <t>0.013301282051282004 +/- 0.005247292923295294</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0007478632478632897 +/- 0.00099077120678377</t>
+          <t>0.0012820512820512775 +/- 0.0007994994416183607</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.03210470085470084 +/- 0.0012964381516572406</t>
+          <t>-0.00021367521367521292 +/- 0.0002616976220922189</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.023237179487179405 +/- 0.001571094142078279</t>
+          <t>0.0024572649572649485 +/- 0.0012909237151276208</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.00010683760683757315 +/- 0.0015628994485393328</t>
+          <t>-0.002510683760683785 +/- 0.0017563335708091787</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.015651709401709457 +/- 0.0015855579144931386</t>
+          <t>0.008547008547008517 +/- 0.002041129612664822</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-5.341880341879213e-05 +/- 0.0008429344998963596</t>
+          <t>0.00010683760683760646 +/- 0.0005233952441844379</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.018269230769230704 +/- 0.002647331558411073</t>
+          <t>0.0003739316239316226 +/- 0.0008292828363386735</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.0043269230769230616 +/- 0.0014423076923076872</t>
+          <t>5.341880341880323e-05 +/- 0.0005039519835500305</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.026175213675213582 +/- 0.001372353907977039</t>
+          <t>0.0 +/- 0.00041378027203070546</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5.341880341880323e-05 +/- 0.0001602564102564097</t>
+          <t>-0.0001602564102564097 +/- 0.0002447957102006316</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.0013354700854700807 +/- 0.001126870892613724</t>
+          <t>-0.0008547008547008517 +/- 0.0009002296766214027</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.0016559829059829 +/- 0.0009390168713272908</t>
+          <t>5.341880341880323e-05 +/- 0.0006067209771154117</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-0.00010683760683760646 +/- 0.0005753381204203509</t>
+          <t>0.00042735042735042583 +/- 0.0005233952441844379</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.00010683760683760646 +/- 0.0006672006408545274</t>
+          <t>0.0005876068376068355 +/- 0.0003739316239316226</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00026709401709402726 +/- 0.0006861769539885497</t>
+          <t>-0.0001602564102564097 +/- 0.0002447957102006316</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1901,237 +1901,237 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.0007478632478632785 +/- 0.0007994994416184037</t>
+          <t>0.0005876068376068355 +/- 0.0004437299072071605</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.0008547008547008517 +/- 0.0008679528210081124</t>
+          <t>-0.0006410256410256387 +/- 0.00046569433157485666</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-0.00042735042735042583 +/- 0.0006672006408545273</t>
+          <t>-0.0005876068376068355 +/- 0.00044372990720716054</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.016559829059829 +/- 0.0016377894996534013</t>
+          <t>-0.005822649572649663 +/- 0.0009689293347872324</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-0.00048076923076922906 +/- 0.0001602564102564097</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-0.0005876068376068355 +/- 0.00028766906021017544</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-0.0009615384615384581 +/- 0.0006672006408545274</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.0001602564102564097 +/- 0.00034204723490559964</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>-0.0003205128205128194 +/- 0.0004895914204012632</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.00026709401709401615 +/- 0.00035834422716342655</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
           <t>-0.0003739316239316226 +/- 0.0002447957102006316</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.00021367521367521292 +/- 0.00026169762209221896</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-0.0082799145299145 +/- 0.001269750461966311</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-0.001175213675213671 +/- 0.000887459814414321</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.00042735042735042583 +/- 0.00021367521367521292</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.0007478632478632452 +/- 0.0005948466199604703</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>-0.0003739316239316226 +/- 0.0005368523301880799</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-0.0012820512820512775 +/- 0.0009002296766214027</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>-0.0013354700854700807 +/- 0.000547379848608951</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.00033785017736841536</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>-0.0008547008547008517 +/- 0.00042735042735042583</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.00010683760683760646 +/- 0.0003997497208091804</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.00021367521367521292 +/- 0.0006410256410256387</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-0.0032051282051282493 +/- 0.001013550532105293</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-0.003952991452991506 +/- 0.0011256040334244792</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-0.0003205128205128194 +/- 0.00026169762209221896</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>-0.00042735042735042583 +/- 0.00021367521367521292</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.00026709401709401615 +/- 0.0004924970329750457</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>-0.007478632478632563 +/- 0.0007923288981939783</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>-0.0003739316239316226 +/- 0.0006343131456751001</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>-0.0006410256410256387 +/- 0.0003997497208091804</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>-0.0010683760683760646 +/- 0.0007166884543268531</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>-0.0001602564102564097 +/- 0.0002447957102006316</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>-0.0008012820512820484 +/- 0.00035834422716342655</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-0.0008547008547008517 +/- 0.00042735042735042583</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>0.00042735042735042583 +/- 0.0007850928662766569</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>0.0012820512820512775 +/- 0.0004895914204012632</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0.00042735042735042583 +/- 0.00032051282051281943</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0.0010683760683760646 +/- 0.0007166884543268532</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0.0003205128205128194 +/- 0.00035434025537984913</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
         <is>
           <t>-0.0003739316239316226 +/- 0.0002447957102006316</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0.00010683760683760646 +/- 0.00021367521367521292</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>0.0010149572649572947 +/- 0.0005039519835500693</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>-0.0020299145299145227 +/- 0.0007850928662766569</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0.0014423076923077427 +/- 0.0005368523301881295</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.00023889615144228436</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.004006410256410242 +/- 0.0011012568444491576</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.0003739316239316226 +/- 0.0006343131456751002</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-0.0026709401709401615 +/- 0.0006320598058867088</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>-0.012606837606837562 +/- 0.0022939007001692106</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>-0.006730769230769207 +/- 0.001150676240840702</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0.0009081196581196882 +/- 0.0012193068600976167</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>5.341880341880323e-05 +/- 0.0001602564102564097</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0.0011752136752137265 +/- 0.001388888888888931</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.002564102564102666 +/- 0.0007478632478632452</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-0.002777777777777768 +/- 0.001007903967100061</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-0.009882478632478597 +/- 0.001313928832932564</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-0.0005876068376068355 +/- 0.00044372990720716054</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0.00026709401709401615 +/- 0.0004306761617680834</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-0.0038995726495726357 +/- 0.0013940158494337438</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-0.0006410256410256277 +/- 0.0010895340841010413</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>0.0011752136752137155 +/- 0.0006672006408545735</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>-0.0012820512820512775 +/- 0.0007246079041800474</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.00026709401709401615 +/- 0.000597240378605711</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.0023504273504274197 +/- 0.001533408129744414</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-0.000694444444444442 +/- 0.0007573422477968897</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-0.014529914529914478 +/- 0.002276418349643423</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>0.0008547008547008961 +/- 0.0008344283841781054</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>0.000694444444444442 +/- 0.00034204723490559964</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>5.341880341880323e-05 +/- 0.0009081196581196548</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0.0013354700854701473 +/- 0.000932919294688775</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>0.0011752136752137265 +/- 0.0008547008547009002</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0.0008547008547008627 +/- 0.00042735042735044524</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.0011752136752137155 +/- 0.0004656943315748974</t>
+          <t>-0.0003205128205128194 +/- 0.00042735042735042583</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0008613523235361873</t>
+          <t>-0.0006410256410256387 +/- 0.0003997497208091803</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>-0.00021367521367521292 +/- 0.0003543402553798492</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5.341880341880323e-05 +/- 0.0001602564102564097</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.0009615384615384914 +/- 0.0007478632478632896</t>
+          <t>0.00026709401709401615 +/- 0.00026709401709401615</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-0.00010683760683760646 +/- 0.0007850928662766569</t>
+          <t>-0.00048076923076922906 +/- 0.00028766906021017544</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>-0.0003205128205128194 +/- 0.00026169762209221896</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0031517094017095015 +/- 0.0003739316239316226</t>
+          <t>-0.00021367521367521292 +/- 0.00042735042735042583</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.0003205128205128305 +/- 0.000641025641025661</t>
+          <t>0.00021367521367521292 +/- 0.0004895914204012632</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00023889615144228436</t>
+          <t>-0.00048076923076922906 +/- 0.0003739316239316226</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.0022435897435898132 +/- 0.0012134419542308653</t>
+          <t>0.00010683760683760646 +/- 0.00039974972080918043</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.0005876068376068466 +/- 0.000808373181112281</t>
+          <t>-0.0003739316239316226 +/- 0.0005368523301880799</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.0005876068376068577 +/- 0.001080328441034039</t>
+          <t>-0.00042735042735042583 +/- 0.000575338120420351</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.0006332453825857121 +/- 0.0012664907651715074</t>
+          <t>0.002163588390501359 +/- 0.0009571692425972043</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.002005277044854925 +/- 0.001126868417100918</t>
+          <t>0.0010554089709763014 +/- 0.0010012488633778698</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0015831134564644356 +/- 0.0009730389928541274</t>
+          <t>-0.0007915567282321568 +/- 0.0014403529355098978</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.0005277044854880897 +/- 0.0010814723763545773</t>
+          <t>0.0005277044854882007 +/- 0.0006243883676094783</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0021108179419525364 +/- 0.0013349984845038036</t>
+          <t>0.0013720316622691797 +/- 0.0014199075511423381</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.002216358839050081 +/- 0.0012882908301566044</t>
+          <t>0.001899736147757325 +/- 0.0019055905103185</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.00015831134564643358 +/- 0.00024182457493169984</t>
+          <t>0.00010554089709764458 +/- 0.00021108179419528916</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0012664907651715684 +/- 0.0005876268456812764</t>
+          <t>-0.0003166226912928338 +/- 0.0006757914762462337</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.012717678100263885 +/- 0.002049912886496569</t>
+          <t>0.026649076517150438 +/- 0.0021272447884692655</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.006332453825857553 +/- 0.0018879729625328006</t>
+          <t>0.012559366754617485 +/- 0.0013720316622691277</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0009498680738786791 +/- 0.0009380680123816062</t>
+          <t>0.0027440633245382927 +/- 0.001050118667130968</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.0005277044854881674 +/- 0.0012262744104086943</t>
+          <t>0.001424802110818002 +/- 0.0012719758093080868</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0007915567282322566 +/- 0.0013608228979659729</t>
+          <t>0.0015303430079156356 +/- 0.0006860158311345454</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.008759894459102935 +/- 0.0033474937260482697</t>
+          <t>0.013403693931398463 +/- 0.0023146925804180757</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.0073350923482849995 +/- 0.003213802634002151</t>
+          <t>0.004010554089709817 +/- 0.002930542137607368</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.00042216358839054503 +/- 0.001126868417100945</t>
+          <t>4.4408920985006264e-17 +/- 0.0007462868403024511</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.002110817941952459 +/- 0.0010012488633778405</t>
+          <t>0.0005277044854881896 +/- 0.001028685418977216</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0007387862796834121 +/- 0.0022537368342018488</t>
+          <t>0.004749340369393185 +/- 0.002016356007867301</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.0010554089709762127 +/- 0.0007079898609498065</t>
+          <t>0.0008443271767810456 +/- 0.001400158222841334</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>5.277044854882229e-05 +/- 0.00015831134564646686</t>
+          <t>-0.00015831134564643358 +/- 0.00024182457493169982</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0050131926121372294 +/- 0.0012543392426390336</t>
+          <t>0.003324538258575249 +/- 0.001336041044978595</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.0011609498680738462 +/- 0.0005683551247635201</t>
+          <t>0.0010026385224275124 +/- 0.0007985617915789729</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.0017414248021107802 +/- 0.0013567240245047297</t>
+          <t>-0.00411609498680734 +/- 0.001597123583157948</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.00026385224274410034 +/- 0.0009215962636714162</t>
+          <t>-0.001688654353561958 +/- 0.0009380680123815663</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.0030606860158310933 +/- 0.0010232569619876316</t>
+          <t>-0.0004221635883904673 +/- 0.000738786279683393</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00015831134564646686 +/- 0.0002418245749317507</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-0.005540897097625286 +/- 0.0011131938316479364</t>
+          <t>-0.00807387862796829 +/- 0.001888710307986614</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-0.0010026385224274014 +/- 0.001280703018418129</t>
+          <t>0.0011081794195251238 +/- 0.0010136872143693123</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.0010026385224274014 +/- 0.0009276198327834723</t>
+          <t>0.001688654353562069 +/- 0.0004600421048591611</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.0010554089709762238 +/- 0.0005780713007969929</t>
+          <t>0.003324538258575238 +/- 0.0010567274086807862</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.00047493403693940064 +/- 0.0001583113456464669</t>
+          <t>0.0003166226912929337 +/- 0.0002585213448848153</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.0005804749340370008 +/- 0.0004978354159396873</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.00021108179419530027 +/- 0.0008574183012808641</t>
+          <t>-0.00015831134564640026 +/- 0.0005804749340369625</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.0026385224274406704 +/- 0.0014547808709330086</t>
+          <t>0.0022691292875989923 +/- 0.001108179419525035</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-0.000844327176780979 +/- 0.0004221635883904895</t>
+          <t>0.0008443271767810789 +/- 0.0004221635883905117</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.0008443271767810901 +/- 0.0003500395557103226</t>
+          <t>-0.0017941952506595805 +/- 0.0004836491498633997</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.0017941952506595916 +/- 0.0015689782319069769</t>
+          <t>-0.005910290237466964 +/- 0.0009078971258092228</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.0014248021108179021 +/- 0.0005303364443863118</t>
+          <t>0.0008443271767810678 +/- 0.0006332453825857639</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.0003693931398417227 +/- 0.0006266143581550663</t>
+          <t>-0.00021108179419523365 +/- 0.0003500395557103461</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.000844327176780979 +/- 0.0007897957544641344</t>
+          <t>-0.0011081794195250238 +/- 0.0008970976253298171</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.0017941952506595805 +/- 0.0009200842097183223</t>
+          <t>0.00031662269129291155 +/- 0.0009498680738786483</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-0.0037994722955144835 +/- 0.0007000791114206838</t>
+          <t>-0.005329815303430019 +/- 0.0016084169555808236</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.004591029023746651 +/- 0.001227409324497429</t>
+          <t>-0.0011081794195250128 +/- 0.0017414248021108303</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-0.011978891820580418 +/- 0.002214473378190748</t>
+          <t>-0.02079155672823214 +/- 0.0033474937260482727</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0010026385224274903 +/- 0.0010672162752589404</t>
+          <t>0.0010554089709763127 +/- 0.0009140109802474351</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.00010554089709766679 +/- 0.0009078971258092692</t>
+          <t>0.0026912928759894815 +/- 0.0007985617915789516</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.0005277044854881008 +/- 0.0005780713007970132</t>
+          <t>0.00010554089709764458 +/- 0.00039489787723210576</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.0011609498680739238 +/- 0.0016316226737456711</t>
+          <t>0.0010026385224274903 +/- 0.0018499786958267044</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0034300791556728604 +/- 0.0015698654122051103</t>
+          <t>0.004116094986807439 +/- 0.001101879314924608</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-0.0049076517150395405 +/- 0.0012274093244974012</t>
+          <t>-0.020580474934036884 +/- 0.0014547808709330086</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0008443271767810568 +/- 0.0017848585250963259</t>
+          <t>-0.0049076517150395075 +/- 0.0022642150873799422</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-0.00026385224274405594 +/- 0.00026385224274405594</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>-0.00031662269129285604 +/- 0.00048364914986341904</t>
+          <t>0.00026385224274411145 +/- 0.0002638522427441115</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-0.011134564643799439 +/- 0.0015376044627264918</t>
+          <t>-0.010606860158311271 +/- 0.0007254737247950995</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.0013192612137202687 +/- 0.0030337271454997108</t>
+          <t>-0.01124010554089704 +/- 0.002214473378190747</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.006543535620052721 +/- 0.0016886543535619934</t>
+          <t>-0.0005277044854880674 +/- 0.0014547808709330127</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,77 +2506,77 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-0.0025857519788917483 +/- 0.0004978354159396485</t>
+          <t>0.00042216358839055614 +/- 0.000775564034654322</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.0018997361477573027 +/- 0.0007897957544641611</t>
+          <t>0.008759894459102958 +/- 0.002420547744840045</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-0.0003166226912928227 +/- 0.0012079707801857212</t>
+          <t>-0.008548812664907613 +/- 0.0015618626476990671</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>-0.0004749340369393007 +/- 0.00028417756238176007</t>
+          <t>0.0013720316622691908 +/- 0.0006757914762462146</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.0017941952506596915 +/- 0.0007158131908311428</t>
+          <t>0.0005804749340369786 +/- 0.0009276198327835014</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.007968337730870656 +/- 0.001642678882984</t>
+          <t>-0.002796833773087004 +/- 0.0008525326871452988</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-0.017361477572559313 +/- 0.0028461818596647688</t>
+          <t>-0.02506596306068596 +/- 0.00237467018469658</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.0017414248021107692 +/- 0.0008525326871452803</t>
+          <t>0.0014775725593668132 +/- 0.0011018793149245804</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00010554089709764458 +/- 0.00021108179419528916</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.0021108179419525473 +/- 0.001396174834334854</t>
+          <t>-0.00010554089709760017 +/- 0.0007387862796833915</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.0011609498680738351 +/- 0.0010763101875657574</t>
+          <t>0.0008970976253298901 +/- 0.0004121503786758255</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.00010554089709767789 +/- 0.0006154038939151017</t>
+          <t>0.0017941952506596915 +/- 0.00048364914986339963</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.002427440633245348 +/- 0.0013801263145775268</t>
+          <t>0.0015303430079156243 +/- 0.0009571692425972032</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.0005804749340370008 +/- 0.0007628935247916268</t>
+          <t>0.0011609498680739572 +/- 0.0005170426897695219</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-0.0006332453825857231 +/- 0.0008106750129676637</t>
+          <t>0.0029023746701847485 +/- 0.001113193831647963</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>-0.0013192612137202797 +/- 0.0005899915507914848</t>
+          <t>0.00010554089709764458 +/- 0.00021108179419528916</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.0006860158311345454 +/- 0.0005804749340369231</t>
+          <t>0.0005277044854881896 +/- 0.00040875813680292517</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.00010554089709760017 +/- 0.00046004210485919167</t>
+          <t>0.00010554089709764458 +/- 0.00021108179419528916</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-0.0007387862796833456 +/- 0.0010340853795390685</t>
+          <t>0.0007915567282322566 +/- 0.0005899915507915145</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2616,37 +2616,37 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.00010554089709767789 +/- 0.0004600421048592121</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.0013720316622690798 +/- 0.0009200842097183451</t>
+          <t>0.0009498680738786903 +/- 0.0010763101875657544</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>-0.0011081794195250349 +/- 0.0008327036326152539</t>
+          <t>0.0028496042216359374 +/- 0.0012969082561946582</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>-0.00010554089709760017 +/- 0.00046004210485919167</t>
+          <t>-5.2770448548788984e-05 +/- 0.0003693931398417132</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.00010554089709767789 +/- 0.0008106750129676911</t>
+          <t>0.0020580474934037475 +/- 0.0006860158311345454</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.001424802110817891 +/- 0.0019892429366723903</t>
+          <t>0.002216358839050192 +/- 0.0014120409667820017</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>6.661338147750939e-17 +/- 0.001179983101583019</t>
+          <t>0.005540897097625374 +/- 0.001360822897965977</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0008771929824560653 +/- 0.0010168441332780393</t>
+          <t>0.0029605263157894356 +/- 0.001254991572616197</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,92 +2666,92 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.0012061403508771273 +/- 0.0008771929824561432</t>
+          <t>0.0037280701754385803 +/- 0.00087719298245615</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.0007675438596491558 +/- 0.0007020969558588641</t>
+          <t>0.0022478070175438124 +/- 0.0015785285141324628</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.00021929824561406353 +/- 0.0008907936847188479</t>
+          <t>0.0032346491228069764 +/- 0.0013305549451218905</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.3306690738754695e-17 +/- 0.0004903657845394042</t>
+          <t>0.0023574561403508333 +/- 0.0008511060688739289</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0008223684210525772 +/- 0.001075735574032257</t>
+          <t>0.003344298245613997 +/- 0.0015593709049701735</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0005482456140350033 +/- 0.00024518289226969594</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0026315789473683737 +/- 0.0008057532048628863</t>
+          <t>0.005317982456140302 +/- 0.0010416666666666588</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.0008771929824561986 +/- 0.001475178075337031</t>
+          <t>0.006633771929824528 +/- 0.0025883929022177433</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.00010964912280707617 +/- 0.0014254385964912173</t>
+          <t>0.007785087719298212 +/- 0.0019736842105263124</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.0004934210526315264 +/- 0.0008296461595625678</t>
+          <t>0.005317982456140314 +/- 0.0014721185945282403</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0007127192982455455 +/- 0.000737589037668498</t>
+          <t>0.0012061403508771384 +/- 0.0009108140200568029</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0003837719298245168 +/- 0.0006956456984895286</t>
+          <t>-0.0009320175438597089 +/- 0.0014515572691747496</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.013651315789473751 +/- 0.0015593709049701574</t>
+          <t>-0.009813596491228104 +/- 0.0022397695412078454</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.0006030701754385804 +/- 0.0012123544072091953</t>
+          <t>0.005866228070175406 +/- 0.0012271397634648822</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.003947368421052588 +/- 0.0013384381157602663</t>
+          <t>-4.4408920985006264e-17 +/- 0.00145052155211874</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.0010964912280701177 +/- 0.0009495892585355636</t>
+          <t>0.00021929824561398581 +/- 0.0017197792918155828</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.00010964912280705396 +/- 0.0007675438596491082</t>
+          <t>-0.00010964912280706507 +/- 0.0011447704505384232</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.000986842105263086 +/- 0.0005904785972735184</t>
+          <t>-0.0010416666666667074 +/- 0.0013305549451218964</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -2761,62 +2761,62 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0008771929824560986 +/- 0.0011809571945470307</t>
+          <t>0.0027412280701754055 +/- 0.0012259144613486037</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.0027960526315789157 +/- 0.0007127192982456342</t>
+          <t>0.002357456140350822 +/- 0.0013214880255695233</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.0007675438596490558 +/- 0.000502475405148647</t>
+          <t>0.0029057017543859254 +/- 0.001097860986540624</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.00027412280701749614 +/- 0.0006601751413811338</t>
+          <t>0.0008223684210525994 +/- 0.0008924791993475458</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.0005482456140350256 +/- 0.0004903657845394042</t>
+          <t>0.0020285087719297823 +/- 0.0011249059500374622</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.000274122807017485 +/- 0.0003677743384045315</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.0011513157894737168 +/- 0.0007925894898465664</t>
+          <t>-0.0009320175438596757 +/- 0.0008857178959103054</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.0070175438596490666 +/- 0.0013826228303638756</t>
+          <t>0.0057017543859648745 +/- 0.0016300513977323058</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.005921052631578905 +/- 0.001269280362148069</t>
+          <t>0.008004385964912254 +/- 0.0016300513977322967</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0006030701754385359 +/- 0.0004554070100283721</t>
+          <t>0.004111842105263131 +/- 0.0012073857206987436</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0004385964912280049 +/- 0.00032894736842101755</t>
+          <t>-1.1102230246251566e-17 +/- 0.00024518289226969594</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0007127192982455344 +/- 0.0003510484779294199</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.0014802631578947011 +/- 0.0010416666666666489</t>
+          <t>0.009210526315789424 +/- 0.0010630876880298949</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.00526315789473678 +/- 0.0009558988911273449</t>
+          <t>0.008991228070175383 +/- 0.000890793684718841</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>5.4824561403488126e-05 +/- 0.0002952392986367314</t>
+          <t>-5.482456140351033e-05 +/- 0.000164473684210531</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.0002741228070174739 +/- 0.0004420097449724726</t>
+          <t>0.00010964912280696515 +/- 0.0006847585524559398</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0011513157894736058 +/- 0.000572385225269235</t>
+          <t>0.001480263157894679 +/- 0.001012400510560286</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>0.0012061403508771273 +/- 0.0005904785972735143</t>
+          <t>0.009978070175438558 +/- 0.0010344277557079716</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.00043859649122802714 +/- 0.000477949445563633</t>
+          <t>-0.000822368421052655 +/- 0.0005617845814670993</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.0002192982456139969 +/- 0.00026858440162091577</t>
+          <t>-0.00016447368421056429 +/- 0.0010416666666666504</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.0016995614035087091 +/- 0.0008296461595626089</t>
+          <t>0.006743421052631549 +/- 0.001751814178582271</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0009320175438595868 +/- 0.0007772723069494298</t>
+          <t>-0.0012609649122807375 +/- 0.00042819351293349104</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0012061403508771495 +/- 0.0012210009567609566</t>
+          <t>-0.0006578947368421573 +/- 0.001677309050523948</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.0012609649122807375 +/- 0.0007375890376685358</t>
+          <t>-0.0018640350877193513 +/- 0.001495414659757227</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.0017543859649123306 +/- 0.0006393587603997222</t>
+          <t>-0.0012609649122807375 +/- 0.0006956456984895769</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.0004385964912281048 +/- 0.0008771929824561264</t>
+          <t>-0.000986842105263186 +/- 0.0005904785972735369</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>5.4824561403499225e-05 +/- 0.00016447368421049772</t>
+          <t>-0.00010964912280702066 +/- 0.00021929824561404133</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.002686403508771984 +/- 0.0012123544072092129</t>
+          <t>0.000274122807017485 +/- 0.0007456946550841523</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>-0.00021929824561407464 +/- 0.0007020969558588485</t>
+          <t>0.00405701754385962 +/- 0.0013912913969791108</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.0035087719298246165 +/- 0.0007436765332373967</t>
+          <t>0.006633771929824528 +/- 0.0023318169208483147</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.0006030701754386359 +/- 0.001459816552159475</t>
+          <t>0.0003837719298245168 +/- 0.0012023965021634349</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.000493421052631593 +/- 0.00045540701002841615</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.00027412280701749614 +/- 0.00027412280701749614</t>
+          <t>-5.482456140353254e-05 +/- 0.0003837719298245374</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.0006578947368420351 +/- 0.0005371688032419018</t>
+          <t>-5.482456140351033e-05 +/- 0.000164473684210531</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.00027412280701750725 +/- 0.0010183210318534253</t>
+          <t>0.007785087719298212 +/- 0.0019274556832507774</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.0006578947368421351 +/- 0.0009108140200568176</t>
+          <t>0.00032894736842102866 +/- 0.0008563870258669379</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,42 +2951,42 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-0.0008771929824561653 +/- 0.00043859649122808265</t>
+          <t>-0.001480263157894779 +/- 0.0005509800230877838</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-0.0015350877192982892 +/- 0.0007675438596491446</t>
+          <t>-0.0018640350877193513 +/- 0.000657894736842124</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-0.00021929824561406353 +/- 0.001074337606483842</t>
+          <t>0.001096491228070129 +/- 0.0014913893101683616</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.00027412280701749614 +/- 0.00027412280701749614</t>
+          <t>-0.000493421052631593 +/- 0.000164473684210531</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.001315789473684248 +/- 0.0007020969558588849</t>
+          <t>0.0009868421052630972 +/- 0.0008771929824561333</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0.00027412280701749614 +/- 0.0004420097449724726</t>
+          <t>0.0065241228070174965 +/- 0.001284580538800449</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0.0006578947368420573 +/- 0.0011182060336826177</t>
+          <t>0.0006030701754385359 +/- 0.0009320175438596345</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0.0001644736842104755 +/- 0.00042819351293344127</t>
+          <t>-0.0024671052631579536 +/- 0.0006601751413811523</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2996,62 +2996,62 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>-0.0016995614035088201 +/- 0.0007537131077230214</t>
+          <t>-0.0011513157894737168 +/- 0.0005172138778539952</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>-0.0005482456140351033 +/- 0.0005482456140351033</t>
+          <t>-0.001973684210526361 +/- 0.0007436765332374131</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-0.0010416666666666964 +/- 0.0006226873186184689</t>
+          <t>0.002192982456140302 +/- 0.0006486929586732219</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-0.002521929824561475 +/- 0.00055910301684133</t>
+          <t>-0.0007127192982456676 +/- 0.0011513157894736806</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>-0.0012061403508772273 +/- 0.0006847585524559841</t>
+          <t>-0.0009320175438596757 +/- 0.00042819351293349104</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-0.0016995614035088201 +/- 0.0008651169867357428</t>
+          <t>-0.002192982456140413 +/- 0.0006486929586732219</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>-0.000164473684210531 +/- 0.00025123770257434047</t>
+          <t>-0.00010964912280702066 +/- 0.00021929824561404133</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
+          <t>-0.00010964912280703176 +/- 0.0004102694503041541</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>-5.482456140353254e-05 +/- 0.0003837719298245374</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>0.0001644736842104977 +/- 0.0002512377025742896</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.000328947368421062 +/- 0.0003636649989424884</t>
+          <t>-0.00010964912280703176 +/- 0.0005371688032419153</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-0.0018640350877193513 +/- 0.000657894736842124</t>
+          <t>0.0004934210526315374 +/- 0.0012123544072091962</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3061,37 +3061,37 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0001644736842104977 +/- 0.0002512377025742896</t>
+          <t>0.00010964912280698735 +/- 0.0004779494455636406</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>5.482456140346592e-05 +/- 0.000712719298245595</t>
+          <t>5.482456140345482e-05 +/- 0.000865116986735697</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.0020833333333333927 +/- 0.00041026945030417193</t>
+          <t>-0.0019188596491228616 +/- 0.0008581401229440227</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00010964912280699845 +/- 0.0002192982456139969</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.003015350877193046 +/- 0.0007042342422513632</t>
+          <t>-0.004276315789473739 +/- 0.0011447704505384317</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>-0.0018092105263158409 +/- 0.0007772723069494643</t>
+          <t>-0.002850877192982504 +/- 0.0010630876880298845</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.0015899122807017997 +/- 0.00038377192982457235</t>
+          <t>-0.00038377192982460564 +/- 0.0008857178959102636</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.006909894969596431 +/- 0.002101335302238599</t>
+          <t>-0.003537866224433417 +/- 0.0023217247097844494</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.007794361525704774 +/- 0.001953631514325286</t>
+          <t>-0.014372581536760687 +/- 0.0018166585655229309</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.005140961857379745 +/- 0.0013995565396541852</t>
+          <t>-0.008678828081813228 +/- 0.0018672576842514604</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.00011055831951353178 +/- 0.0009183663751153378</t>
+          <t>0.006909894969596431 +/- 0.0009332196249935906</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.006965174129353202 +/- 0.001662055984341939</t>
+          <t>-0.006522940851299131 +/- 0.001673050961904</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.005306799336650059 +/- 0.001190749542760526</t>
+          <t>0.0057490326147042305 +/- 0.0023737877892298274</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0001105583195135429 +/- 0.00022111663902708577</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.007131011608623628 +/- 0.0014082630406696448</t>
+          <t>0.0032061912658927437 +/- 0.0020053462849327773</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-0.001271420674405732 +/- 0.001962994019299588</t>
+          <t>0.00497512437810943 +/- 0.0024844892265609873</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.009784411276948657 +/- 0.0026860211416818765</t>
+          <t>0.010116086235489175 +/- 0.0028835381660021926</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-0.00011055831951352068 +/- 0.0012311253428037951</t>
+          <t>-0.003040353786622463 +/- 0.0014467940661473417</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.0029850746268656582 +/- 0.0010252756766717147</t>
+          <t>-0.018407960199005 +/- 0.0017136539524599149</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.013211719181868375 +/- 0.0025506405738107848</t>
+          <t>-0.013266998341625258 +/- 0.0017997590487672341</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.017302377003869572 +/- 0.0026401224845239357</t>
+          <t>0.013930348258706416 +/- 0.002923008085439986</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.017799889441680518 +/- 0.0025548302948128895</t>
+          <t>0.018573797678275238 +/- 0.003373387794890541</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.004201216141514741 +/- 0.0011382675667205035</t>
+          <t>-0.000497512437810943 +/- 0.001451012133599406</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.008955223880596974 +/- 0.002194519982452086</t>
+          <t>-0.011111111111111172 +/- 0.002325012807607849</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.0006080707573244859 +/- 0.0011971480280656506</t>
+          <t>0.011719181868435546 +/- 0.0017963600673600714</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.003593145384190144 +/- 0.0014255165238504775</t>
+          <t>-0.004090657822001143 +/- 0.0015279463749127322</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0005527915975677145 +/- 0.0005527915975677145</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.0016583747927031989 +/- 0.0008199224419122282</t>
+          <t>0.005472636815920373 +/- 0.0011713443947162518</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.0033167495854062867 +/- 0.0016021422604963376</t>
+          <t>-0.00259812050856828 +/- 0.001421222789627719</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.001768933112216753 +/- 0.00169121708576879</t>
+          <t>0.0005527915975677145 +/- 0.001105583195135429</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0013266998341625812 +/- 0.0009315809588918488</t>
+          <t>0.004256495301271401 +/- 0.0021840515494901402</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.0014925373134328291 +/- 0.0009266475740320693</t>
+          <t>0.005140961857379745 +/- 0.001079006152346216</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.0001105583195135429 +/- 0.00022111663902708577</t>
+          <t>5.527915975677145e-05 +/- 0.00016583747927031433</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-0.0030956329463792008 +/- 0.0011648041738919503</t>
+          <t>0.014593698175787661 +/- 0.002143805354302402</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.0031509121061359725 +/- 0.0008581633331265868</t>
+          <t>-0.008291873963515828 +/- 0.0016021422604963376</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.0009397457158651146 +/- 0.0007437050330057297</t>
+          <t>-0.004422332780541771 +/- 0.0015239412661238873</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.001105583195135429 +/- 0.0010488483118303036</t>
+          <t>-0.0054726368159204505 +/- 0.0026215380213111157</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0006633499170812685 +/- 0.0005953747713802816</t>
+          <t>0.0007186290768380288 +/- 0.00043174403957471635</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.00027639579878385723 +/- 0.00044567483406846394</t>
+          <t>5.527915975677145e-05 +/- 0.0003869541182974001</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.008236594803758945 +/- 0.0014297973638891658</t>
+          <t>0.003593145384190144 +/- 0.0014467940661473013</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.006080707573244859 +/- 0.0016766999323496994</t>
+          <t>-0.012658927584300771 +/- 0.0015723010119765425</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.0004422332780541716 +/- 0.00022111663902708577</t>
+          <t>-0.0007186290768380288 +/- 0.00043174403957471635</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.00033167495854062866 +/- 0.0003666804632786495</t>
+          <t>-0.0009397457158651146 +/- 0.001212366622413555</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.0004975124378109541 +/- 0.0009717189514232847</t>
+          <t>-0.002377003869541172 +/- 0.0010503040353786576</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.0020453289110005436 +/- 0.001285760458774235</t>
+          <t>-0.002708678828081812 +/- 0.002271832237483103</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.0008291873963515827 +/- 0.0004456748340684846</t>
+          <t>0.002266445550027629 +/- 0.0007991615420011551</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.0014925373134328846 +/- 0.0004317440395747661</t>
+          <t>0.0031509121061359725 +/- 0.0011608623548922004</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0006633499170812795 +/- 0.0006904364840683979</t>
+          <t>-0.007075732448866856 +/- 0.0016730509619039787</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0003869541182974223 +/- 0.0009904075659021325</t>
+          <t>-0.0015478164731896004 +/- 0.0009183663751153165</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.0026533996683251295 +/- 0.0007739082365948224</t>
+          <t>0.011276948590381374 +/- 0.0023479005618126264</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>-0.004698728579325573 +/- 0.0017172166464354888</t>
+          <t>0.014814814814814748 +/- 0.0025186922608942987</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.002266445550027696 +/- 0.0013641749783585885</t>
+          <t>0.00033167495854062866 +/- 0.0009315809588917987</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.0010503040353786574 +/- 0.000799161542001155</t>
+          <t>-0.001990049751243772 +/- 0.0011382675667205035</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.0001105583195135429 +/- 0.00048191254212721435</t>
+          <t>0.0004422332780541716 +/- 0.0005416229392555372</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.012437810945273575 +/- 0.0023485512201490218</t>
+          <t>0.0055279159756771445 +/- 0.0014415041249757035</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.0029850746268656582 +/- 0.0008273427057543227</t>
+          <t>-0.013930348258706515 +/- 0.0017091901419281632</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.002321724709784401 +/- 0.0009510586254331219</t>
+          <t>0.021724709784411267 +/- 0.002127350072403991</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.008291873963515828 +/- 0.0023452961233384555</t>
+          <t>0.0027639579878385723 +/- 0.002358289553090265</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-0.0008291873963515717 +/- 0.00044567483406846394</t>
+          <t>-0.0001105583195135429 +/- 0.0004136713528771613</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.00033167495854062866 +/- 0.0003666804632786495</t>
+          <t>0.0007186290768380288 +/- 0.000497512437810943</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>-0.0026533996683250293 +/- 0.000849214565822949</t>
+          <t>0.01265892758430066 +/- 0.0013415877390283628</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.006246545052515285 +/- 0.003008019427399166</t>
+          <t>0.024930901050304034 +/- 0.001755929261942346</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.0039248203427307725 +/- 0.0011713443947162518</t>
+          <t>-0.006578220011055902 +/- 0.0017903963229078815</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,42 +3396,42 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>0.0001105583195135429 +/- 0.00022111663902708577</t>
+          <t>-0.0005527915975677145 +/- 0.0005527915975677145</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>0.0005527915975677477 +/- 0.0012111057103486558</t>
+          <t>-0.00016583747927031433 +/- 0.001212366622413555</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.0029297954671088865 +/- 0.0011608623548922004</t>
+          <t>-0.0001105583195135429 +/- 0.0007739082365948002</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>-0.00027639579878385723 +/- 0.00044567483406846394</t>
+          <t>0.00033167495854062866 +/- 0.00027081146962776856</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0008563810605212817</t>
+          <t>-0.0017689331122166863 +/- 0.000733360926557299</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>0.007186290768380399 +/- 0.0006540718389275389</t>
+          <t>0.007075732448866745 +/- 0.0015790886519718777</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>0.016252072968490915 +/- 0.0012653978045615861</t>
+          <t>-0.0034825870646766456 +/- 0.0023328853339977386</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.002266445550027629 +/- 0.0011449593796134818</t>
+          <t>-0.0029297954671088865 +/- 0.0005555486799956243</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3441,32 +3441,32 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.000699232207886869</t>
+          <t>-0.003040353786622463 +/- 0.0012666046696948503</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.0022111663902709576 +/- 0.0006992322078868865</t>
+          <t>0.0019347705914870006 +/- 0.0009965592248380247</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.0014925373134328733 +/- 0.0007014139049447366</t>
+          <t>0.008291873963515717 +/- 0.0010775892034061824</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.000995024875621886 +/- 0.000849214565822949</t>
+          <t>0.003372028745163058 +/- 0.0023118323566972236</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.0008844665561083653 +/- 0.0005066418678779576</t>
+          <t>-0.011663902708678887 +/- 0.0016666460399868731</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.0012161415146489719 +/- 0.000849214565822949</t>
+          <t>-0.012271973466003372 +/- 0.0018132912622284855</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.001326699834162559 +/- 0.0007079186553270584</t>
+          <t>0.0028192371475953435 +/- 0.0007186290768380288</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.0002211166390270858 +/- 0.00044223327805417153</t>
+          <t>0.0016030956329463719 +/- 0.001247154690180036</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.001105583195135451 +/- 0.00034961610394346963</t>
+          <t>0.0006080707573244859 +/- 0.0006747681379620591</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0.0015478164731896782 +/- 0.0003316749585406731</t>
+          <t>-0.004201216141514685 +/- 0.001289320485316853</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0004975124378109541 +/- 0.0006747681379620781</t>
+          <t>0.002598120508568258 +/- 0.000656403653235924</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.002598120508568369 +/- 0.0007437050330057297</t>
+          <t>0.004809286898839115 +/- 0.001106964311470464</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>0.0032614704256496265 +/- 0.0009397457158651146</t>
+          <t>-0.0021558872305140974 +/- 0.0013641749783585646</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.0002211166390270858 +/- 0.0003666804632786495</t>
+          <t>0.0013819789939192861 +/- 0.00044567483406846394</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.007517965726920916 +/- 0.002100608070757315</t>
+          <t>-0.00033167495854062866 +/- 0.001445737626381643</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>0.0019900497512438386 +/- 0.0010832458785111163</t>
+          <t>-0.0035378662244334056 +/- 0.001335881257445537</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>0.0021558872305141863 +/- 0.0006278505633831305</t>
+          <t>0.006522940851299031 +/- 0.0018631619177835977</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0016265060240963746 +/- 0.0014520446738788078</t>
+          <t>-0.005240963855421732 +/- 0.0008955463100794171</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,92 +3556,92 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.001867469879518069 +/- 0.0007353346756466</t>
+          <t>-0.0006024096385542687 +/- 0.00038099730845403336</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.004939759036144587 +/- 0.0016119383325613982</t>
+          <t>-0.001385542168674736 +/- 0.0009351912467626498</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.0010240963855421615 +/- 0.0006626506024096433</t>
+          <t>-0.0008433734939759408 +/- 0.0009787998077874654</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.000120481927710836 +/- 0.0010364247309689921</t>
+          <t>-0.0001807228915663095 +/- 0.0007153218124721713</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.002048192771084345 +/- 0.0010503370948290913</t>
+          <t>0.0003614457831324858 +/- 0.0009016041895840878</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-6.02409638554291e-05 +/- 0.0001807228915662873</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0018072289156626509 +/- 0.0017038717618952735</t>
+          <t>-0.003674698795180775 +/- 0.0008708935117349942</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.005481927710843382 +/- 0.002590361445783131</t>
+          <t>-0.0028915662650602857 +/- 0.0014706693512932226</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.0065662650602409615 +/- 0.002355568047712895</t>
+          <t>-0.0010240963855422057 +/- 0.001079305594407754</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.006566265060240983 +/- 0.001247729829952307</t>
+          <t>0.001204819277108371 +/- 0.00046662449954306236</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.0029518072289156706 +/- 0.0009880252690877393</t>
+          <t>-0.002951807228915704 +/- 0.001058939507906441</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-0.0016867469879518148 +/- 0.0010007980557732675</t>
+          <t>0.00042168674698790377 +/- 0.0007643721409909265</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.006445783132530136 +/- 0.0025706732883556535</t>
+          <t>-0.002168674698795214 +/- 0.0015287442819818594</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.011987951807228914 +/- 0.0031469778040021544</t>
+          <t>-0.005000000000000049 +/- 0.0027612449726182884</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.0035542168674698948 +/- 0.000628934127042788</t>
+          <t>-0.0003012048192771566 +/- 0.00072539726378267</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.0031927710843373757 +/- 0.0007153218124721666</t>
+          <t>-0.0019277108433735425 +/- 0.0008853577383553567</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.002048192771084334 +/- 0.0012404373663839731</t>
+          <t>0.00018072289156625398 +/- 0.00038573037574894317</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.0031927710843373536 +/- 0.001079305594407778</t>
+          <t>-0.005481927710843404 +/- 0.0009116112018326319</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3651,62 +3651,62 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.004277108433734933 +/- 0.001385542168674709</t>
+          <t>-0.004698795180722937 +/- 0.0023762750510019307</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.003192771084337365 +/- 0.0008955463100794276</t>
+          <t>0.000783132530120434 +/- 0.00027605877680455176</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0003809973084539983</t>
+          <t>-0.0007228915662651159 +/- 0.00036144578313253024</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.00036144578313251907 +/- 0.0004819277108433634</t>
+          <t>0.00012048192771082488 +/- 0.00036144578313253013</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.0011445783132530084 +/- 0.0011253940778475544</t>
+          <t>-0.00048192771084342166 +/- 0.00036144578313255236</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.00042168674698794817 +/- 0.00047049696842811986</t>
+          <t>-0.0005421686746988619 +/- 0.0001807228915662873</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.0003614457831325302 +/- 0.0015523010514126776</t>
+          <t>-0.0019879518072289494 +/- 0.001079305594407767</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.0006024096385542244 +/- 0.0011107884888304665</t>
+          <t>-0.00048192771084342166 +/- 0.00036144578313255236</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0.004337349397590373 +/- 0.0009638554216867574</t>
+          <t>-0.0001807228915662873 +/- 0.0004704969684281269</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0040963855421687016 +/- 0.0011042351072182797</t>
+          <t>0.000903614457831281 +/- 0.0005553942444152182</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.000120481927710836 +/- 0.00036144578313250796</t>
+          <t>-0.0003012048192771455 +/- 0.0003012048192771455</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.0016265060240963857 +/- 0.0006054141940434087</t>
+          <t>-0.0002409638554217164 +/- 0.0002951192461184915</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.0009638554216867545 +/- 0.000722891566265066</t>
+          <t>-0.0004819277108433995 +/- 0.0008433734939759233</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.005361445783132535 +/- 0.0011253940778475687</t>
+          <t>0.0001807228915662429 +/- 0.0010098225671229173</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3731,57 +3731,57 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00042168674698792594 +/- 0.00027605877680455176</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.0008433734939759074 +/- 0.0014306436249443518</t>
+          <t>-0.0012048192771084599 +/- 0.0006024096385542022</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>0.0025903614457831294 +/- 0.0009351912467626648</t>
+          <t>0.00030120481927709 +/- 0.00030120481927709</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.0007831325301204672 +/- 0.0002760587768046026</t>
+          <t>-0.0017469879518072662 +/- 0.0005003990278866445</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.00024096385542168308 +/- 0.0005521175536091229</t>
+          <t>-0.0006024096385542577 +/- 0.0006599066957893568</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.0037349397590361265 +/- 0.0007991866964711836</t>
+          <t>-6.02409638554402e-05 +/- 0.00032440751850209583</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0003614457831325302 +/- 0.0008171481907379897</t>
+          <t>-0.0001807228915663095 +/- 0.0007643721409909363</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.007469879518072287 +/- 0.0022084702144365372</t>
+          <t>-0.0003012048192771566 +/- 0.000673514451054162</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.003554216867469884 +/- 0.000988025269087755</t>
+          <t>-0.006566265060241006 +/- 0.0009505863757867218</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.000120481927710836 +/- 0.00024096385542167202</t>
+          <t>-0.0002409638554217164 +/- 0.0002951192461184915</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.0001807228915662651 +/- 0.0005421686746987829</t>
+          <t>-0.000963855421686799 +/- 0.000817148190737975</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -3791,47 +3791,47 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.0014457831325301318 +/- 0.0007714607514979157</t>
+          <t>0.00024096385542164976 +/- 0.0005521175536091375</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0021686746987951812 +/- 0.0007228915662650512</t>
+          <t>0.00012048192771080268 +/- 0.0007524093973973922</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0043373493975903624 +/- 0.0012286794008657224</t>
+          <t>-0.003795180722891611 +/- 0.0013483752581686422</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.005602409638554217 +/- 0.001924884976948254</t>
+          <t>-0.011325301204819305 +/- 0.0021006741896581575</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>0.000120481927710836 +/- 0.000240963855421672</t>
+          <t>0.00030120481927706775 +/- 0.000673514451054142</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.000120481927710836 +/- 0.00024096385542167202</t>
+          <t>0.000783132530120434 +/- 0.00038573037574894317</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.00024096385542168308 +/- 0.0004819277108433662</t>
+          <t>-0.0006024096385542465 +/- 0.0008082173412650009</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.005843373493975901 +/- 0.00210498857947666</t>
+          <t>-0.01662650602409641 +/- 0.0018311667654904518</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.0016265060240963746 +/- 0.0019806364123823657</t>
+          <t>0.0012650602409638111 +/- 0.0008281763304137012</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,92 +3841,92 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-0.0005421686746987953 +/- 0.0005003990278866445</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>0.0016265060240963857 +/- 0.0005421686746987829</t>
+          <t>-0.000963855421686799 +/- 0.0003995933482355658</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>0.005602409638554229 +/- 0.0019806364123823657</t>
+          <t>-0.005000000000000027 +/- 0.0016398382637127884</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0005421686746988396 +/- 0.00042168674698796877</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.001927710843373487 +/- 0.0010708667972669352</t>
+          <t>-0.0001204819277108804 +/- 0.00045080209479206096</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0.004096385542168668 +/- 0.0014951414031314414</t>
+          <t>-0.003614457831325335 +/- 0.0012048192771084432</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.00042168674698794817 +/- 0.001112420801964995</t>
+          <t>-0.003915662650602447 +/- 0.0012418992848245878</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>0.004216867469879504 +/- 0.0011107884888304606</t>
+          <t>0.00048192771084333287 +/- 0.0005251685474145297</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>6.0240963855418e-05 +/- 0.00018072289156625398</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.00403614457831325 +/- 0.0009732225555062351</t>
+          <t>-0.0011445783132530418 +/- 0.0008708935117349972</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.00957831325301206 +/- 0.0007831325301204801</t>
+          <t>0.00036144578313249685 +/- 0.0004819277108433661</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.0012048192771084265 +/- 0.0012345723814409047</t>
+          <t>0.00024096385542164976 +/- 0.0006143397004328585</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.007590361445783134 +/- 0.001015198767852569</t>
+          <t>0.0007228915662650271 +/- 0.0005902384922368947</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>0.0034939759036144657 +/- 0.00167811906954026</t>
+          <t>0.00012048192771082488 +/- 0.00036144578313253013</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0.0067469879518072375 +/- 0.0011366242327779132</t>
+          <t>0.0017469879518071884 +/- 0.0005683121163889596</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>0.0005421686746987619 +/- 0.00018072289156625398</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.0026506024096385585 +/- 0.0007714607514979297</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-3.3306690738754695e-17 +/- 0.0004666244995430767</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,52 +3936,52 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>0.0024698795180722933 +/- 0.0010589395079064446</t>
+          <t>-0.00048192771084341055 +/- 0.00045080209479206096</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0.004578313253012045 +/- 0.0013524062843761394</t>
+          <t>0.0010240963855421392 +/- 0.0007153218124721563</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-6.02409638554291e-05 +/- 0.0001807228915662873</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-0.0002409638554216942 +/- 0.0006143397004328628</t>
+          <t>-0.0001204819277108582 +/- 0.0002409638554217164</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0028313253012048124 +/- 0.0010451416610179232</t>
+          <t>0.00036144578313249685 +/- 0.0005521175536091229</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.01096385542168673 +/- 0.0013416299669470016</t>
+          <t>0.000963855421686699 +/- 0.0005521175536091205</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0003614457831325746 +/- 0.0002951192461184915</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.0025301204819277224 +/- 0.0007025243246801613</t>
+          <t>-0.0001204819277108693 +/- 0.0005251685474145501</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.0013855421686747138 +/- 0.00047049696842810137</t>
+          <t>-2.2204460492503132e-17 +/- 0.00038099730845403336</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>0.0005421686746987953 +/- 0.0012477298299522935</t>
+          <t>0.0005421686746987509 +/- 0.0005683121163889396</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.00037413148049166847 +/- 0.0005879208979155352</t>
+          <t>5.344735435597325e-05 +/- 0.00028782281171215173</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,27 +4001,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0018172100481026465 +/- 0.000763380911656092</t>
+          <t>5.3447354355962154e-05 +/- 0.00016034206306788645</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.00032068412613570627 +/- 0.00042757883484765</t>
+          <t>-0.0006413682522714348 +/- 0.00021378941742384862</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.0015499732763227913 +/- 0.00016034206306788642</t>
+          <t>-0.004168893639764826 +/- 0.0003206841261357729</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0007482629609834701 +/- 0.0004275788348476972</t>
+          <t>-0.00016034206306785314 +/- 0.0002449265470312734</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0034740780331374175 +/- 0.0005476724086563242</t>
+          <t>0.0005879208979155837 +/- 0.00037413148049173504</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4031,402 +4031,402 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.0012292891501870184 +/- 0.0005371392635553934</t>
+          <t>-0.00438268305718863 +/- 0.0008551576696953445</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.0035275253874933687 +/- 0.0005450582056218882</t>
+          <t>-0.00026723677177975524 +/- 0.0007652496559741397</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.003206841261357618 +/- 0.0006323976251309377</t>
+          <t>-0.0015499732763227803 +/- 0.0009395187510019974</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0014430785676109448 +/- 0.0005879208979155443</t>
+          <t>-0.00016034206306785314 +/- 0.0002449265470312734</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.0008551576696953833 +/- 0.0004898530940626194</t>
+          <t>-0.00016034206306785314 +/- 0.00024492654703127343</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>5.3447354355962154e-05 +/- 0.00016034206306788645</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.002832709780865894 +/- 0.0010154997327632325</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.0011223944414751829 +/- 0.0014231455858572377</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>-0.0023516835916621683 +/- 0.00035452964087173726</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-0.00032068412613570627 +/- 0.0005450582056218708</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>-5.344735435595105e-05 +/- 0.00016034206306785314</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>-0.004863709246392267 +/- 0.0009086050240513083</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-0.0027792624265098433 +/- 0.0008210738372922104</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.00010689470871192431 +/- 0.00021378941742384862</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.00021378941742384862 +/- 0.0003545296408717875</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.00016034206306790865 +/- 0.0004810261892036272</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-5.344735435593995e-05 +/- 0.0002878228117121373</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.0013361838588990427 +/- 0.0008365834229021028</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.00037413148049173504 +/- 0.0003422300501033234</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>-0.0009620523784072188 +/- 0.0003999633764589936</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>-0.0005879208979154948 +/- 0.0003741314804917002</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>-0.0001068947087119021 +/- 0.0002137894174238042</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>-0.00026723677177976636 +/- 0.00035853575267230295</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>5.344735435597325e-05 +/- 0.00028782281171215173</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>-0.0005344735435595327 +/- 0.00033803074934988934</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>-0.00026723677177975524 +/- 0.00026723677177975524</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.00032068412613570627 +/- 0.00026183749254759983</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.001710315339390678 +/- 0.0004659432328744949</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0005344735435596326 +/- 0.00041400142663894704</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-0.000587920897915506 +/- 0.0004439670691030294</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.0010154997327632808 +/- 0.00016034206306788642</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>-0.0001068947087119021 +/- 0.0002137894174238042</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.00026723677177981076 +/- 0.00026723677177981076</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.00010689470871193541 +/- 0.0003206841261357507</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-0.0003206841261357174 +/- 0.0004898530940626001</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-0.0002137894174237931 +/- 0.0004898530940626001</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-0.00016034206306785314 +/- 0.0002449265470312734</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>-0.0018706574024585643 +/- 0.00035853575267235255</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>-0.0005344735435595327 +/- 0.00033803074934988934</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-0.000641368252271457 +/- 0.00039996337645898473</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
           <t>0.00016034206306788645 +/- 0.0002449265470313243</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.008017103153393944 +/- 0.001820351295128407</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0.0027792624265099318 +/- 0.0015267618233122159</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>-0.0064136825227151025 +/- 0.0003380307493498894</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0.000694815606627508 +/- 0.0002449265470313243</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>0.00358097274184932 +/- 0.0008297260660748284</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>-0.0013361838588989428 +/- 0.00026723677177981076</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-0.0019775521111704774 +/- 0.00041743718203670303</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0.0002137894174238597 +/- 0.00042757883484767777</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0.0021913415285943704 +/- 0.0006070452534259941</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0.001977552111170555 +/- 0.0008297260660748263</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>-0.0013361838588989428 +/- 0.00035853575267235255</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>5.3447354355962154e-05 +/- 0.00016034206306788645</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-0.0012292891501870184 +/- 0.0003422300501033234</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0.0006413682522715458 +/- 0.00039996337645902035</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-0.0008551576696952834 +/- 0.0002618374925476542</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>0.002351683591662246 +/- 0.0004275788348476583</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>0.0023516835916622568 +/- 0.0007249951879342835</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>-0.0003206841261357174 +/- 0.00035452964087173726</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>0.00016034206306788645 +/- 0.0002449265470313243</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>-0.0009086050240512455 +/- 0.0002449265470313243</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0.0016034206306788311 +/- 0.00041400142663893273</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-5.344735435593995e-05 +/- 0.0002878228117121373</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.001389631213254905 +/- 0.0002618374925476542</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0029396044895778186 +/- 0.0006435913724635216</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-0.00016034206306784205 +/- 0.00048102618920361253</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>0.0017103153393907555 +/- 0.001063588922615299</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>-0.0013361838588989428 +/- 0.0004309063467824141</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>0.002405130946018197 +/- 0.00043090634678239343</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>-0.000641368252271457 +/- 0.0004659432328744643</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.0009086050240513565 +/- 0.0002449265470313243</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-0.000106894708711891 +/- 0.0004659432328744516</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>0.0005879208979155837 +/- 0.00016034206306788642</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>-0.00016034206306785314 +/- 0.0002449265470312734</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.0007482629609834701 +/- 0.0002618374925476542</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0.00037413148049173504 +/- 0.0003422300501033234</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>-0.0008551576696952945 +/- 0.0004898530940626292</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>-0.001068947087119132 +/- 0.0005344735435596215</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>0.00048102618920365937 +/- 0.00028782281171217444</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>-0.0002137894174238042 +/- 0.00026183749254759983</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>-0.00032068412613570627 +/- 0.00026183749254759983</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
         <is>
           <t>-0.0001068947087119021 +/- 0.0002137894174238042</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>0.0010154997327632698 +/- 0.0005042213325524655</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.00021378941742387081 +/- 0.0006413682522715107</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>0.0013361838588990317 +/- 0.0006435913724635077</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-0.002725815072153892 +/- 0.0009984789787423358</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>5.3447354355962154e-05 +/- 0.00016034206306788645</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>-0.0010154997327631698 +/- 0.00044396706910307355</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>-0.0009620523784072077 +/- 0.00021378941742384862</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>-0.0011223944414750942 +/- 0.0003741314804917351</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>0.0004275788348477194 +/- 0.0006675572419453152</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>0.0009086050240513565 +/- 0.0008959409200556032</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>-0.0008017103153393212 +/- 0.00035853575267235255</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.0009620523784073187 +/- 0.00021378941742384862</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>0.0010154997327632587 +/- 0.0006948156066274721</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>0.0016568679850347823 +/- 0.0009694472018822377</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>0.0005344735435596215 +/- 0.0004140014266389757</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0.0015499732763228692 +/- 0.0004439670691030294</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>-0.0001068947087118688 +/- 0.0006232979043126839</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>-0.0004275788348476417 +/- 0.0007090592817435247</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>-0.0010154997327631698 +/- 0.00044396706910307355</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>0.0018172100481026576 +/- 0.0005951645497412982</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>0.00037413148049173504 +/- 0.0004174371820367215</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>-0.0012292891501870184 +/- 0.0003422300501033234</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>-5.344735435595105e-05 +/- 0.00016034206306785314</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>0.00016034206306788645 +/- 0.00034223005010332335</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>-0.0006413682522714681 +/- 0.0005756456234243117</t>
+          <t>-0.0003206841261357396 +/- 0.0004898530940625978</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>-0.0002137894174237931 +/- 0.00035452964087173726</t>
+          <t>-0.00016034206306785314 +/- 0.0002449265470312734</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>0.00016034206306788645 +/- 0.0002449265470313243</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.0008551576696953833 +/- 0.000595164549741324</t>
+          <t>-0.0002137894174238042 +/- 0.00026183749254759983</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0.0025120256547301323 +/- 0.0005879208979155493</t>
+          <t>1.1102230246251566e-17 +/- 0.0002390238351148769</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.002779262426509921 +/- 0.00032068412613577284</t>
+          <t>0.00037413148049173504 +/- 0.0002449265470313243</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.003022407503908242 +/- 0.001036985343519156</t>
+          <t>-0.002397081813444546 +/- 0.0011224939670942075</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,92 +4446,92 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.0019801980198020154 +/- 0.0009263360518306895</t>
+          <t>-0.0039603960396039865 +/- 0.0010211525764599067</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.0031787389265242605 +/- 0.0019836233778712225</t>
+          <t>-0.009640437727983352 +/- 0.0014031174588677723</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.002084418968212642 +/- 0.0011176451583911888</t>
+          <t>0.002970297029702951 +/- 0.0016321479690845158</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.0006774361646691319 +/- 0.0009900990099010016</t>
+          <t>0.0027618551328816967 +/- 0.0012560678262838925</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.003074517978113633 +/- 0.0010538691201749234</t>
+          <t>0.002292860865033852 +/- 0.0014403621637399963</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0005211047420531356 +/- 0.0</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0007816571130797034 +/- 0.0010742849467476616</t>
+          <t>-0.005732152162584725 +/- 0.0018349991518143798</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.02209484106305365 +/- 0.0023788873810345673</t>
+          <t>0.03376758728504427 +/- 0.0025929870358780012</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.012037519541427798 +/- 0.002771669858670604</t>
+          <t>0.028764981761334008 +/- 0.0028332000456629883</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0026055237102657223 +/- 0.0017125249322725443</t>
+          <t>0.0016154247003647537 +/- 0.0013275392603290242</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.0013548723293381637 +/- 0.0010211525764598885</t>
+          <t>5.2110474205291354e-05 +/- 0.0016053071183688814</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.008077123501823902 +/- 0.001194000962729512</t>
+          <t>0.001459093277748813 +/- 0.0015067047727776066</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.022407503908285532 +/- 0.003369094293954067</t>
+          <t>0.030276185513288135 +/- 0.0037825887324563915</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.004481500781657077 +/- 0.0015317288646898332</t>
+          <t>0.022459614382490868 +/- 0.0024491922876498213</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.010057321521625895 +/- 0.0009336358971948545</t>
+          <t>0.0018759770713913215 +/- 0.0017470614501553206</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.007243355914538852 +/- 0.001605307118368868</t>
+          <t>-0.002970297029702984 +/- 0.0007387934798727129</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.0053673788431474415 +/- 0.0012342594353649853</t>
+          <t>0.015164147993746723 +/- 0.0023472862177290575</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.0046378322042730956 +/- 0.0014450677044150085</t>
+          <t>-0.0021886399166232695 +/- 0.001611216762244953</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4541,62 +4541,62 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.001198540906722212 +/- 0.0010692175366692298</t>
+          <t>0.008389786347055728 +/- 0.0013275392603290157</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.005836373110995341 +/- 0.0016112167622449628</t>
+          <t>-0.005784262636790027 +/- 0.0008222894131349131</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.0012506513809275254 +/- 0.001073020337778704</t>
+          <t>0.00015633142261594067 +/- 0.0006187775970316586</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.00036477331943718383 +/- 0.0008089721050682588</t>
+          <t>-0.0004168837936425307 +/- 0.000510576288229959</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.0021365294424178895 +/- 0.0008858780614903678</t>
+          <t>0.0028660760812923235 +/- 0.0007087790780998282</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.00036477331943719494 +/- 0.00033366984040816253</t>
+          <t>0.00010422094841062712 +/- 0.00020844189682125421</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.0025013027618550733 +/- 0.0008005362947231612</t>
+          <t>0.008910891089108896 +/- 0.001913951815758938</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-0.009484106305367413 +/- 0.0009552007701835957</t>
+          <t>-0.009640437727983342 +/- 0.0021892601915164097</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>-0.007139134966128213 +/- 0.0011663902702240443</t>
+          <t>-0.0024491922876498594 +/- 0.0013397561367568818</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.007712350182386696 +/- 0.001974705088222636</t>
+          <t>-0.008910891089108941 +/- 0.0011756658856360918</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-0.0007295466388744342 +/- 0.00041688379364255565</t>
+          <t>-0.0010422094841063378 +/- 0.0004660902506513715</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.0005211047420531356 +/- 0.00023304512532566093</t>
+          <t>0.00031266284523188135 +/- 0.0004776003850917864</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.006982803543512273 +/- 0.0012806884551792022</t>
+          <t>-0.005784262636790017 +/- 0.0015711113529631633</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.0056279312141740865 +/- 0.0014516298360796296</t>
+          <t>-0.0025534132360604646 +/- 0.002335688882857212</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.0005211047420531356 +/- 0.0004036459975203012</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.00020844189682125424 +/- 0.0005802776824210359</t>
+          <t>5.211047420531356e-05 +/- 0.00015633142261594067</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.006670140698280325 +/- 0.0013548723293381928</t>
+          <t>0.0033350703491401568 +/- 0.003171469318333077</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>-0.006461698801459126 +/- 0.0019386217027345717</t>
+          <t>-0.005002605523710302 +/- 0.0015667844062921302</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.00010422094841062712 +/- 0.00031266284523188135</t>
+          <t>-0.0005732152162584714 +/- 0.0004916092304354835</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.0013548723293381637 +/- 0.0008139916285468088</t>
+          <t>0.00036477331943719494 +/- 0.0011428719228484298</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.005940594059405979 +/- 0.0011928632769420985</t>
+          <t>0.0010422094841062823 +/- 0.0009025798893011243</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.002032308494007251 +/- 0.0010793285657742543</t>
+          <t>0.00010422094841060492 +/- 0.000865724217083705</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.0003126628452319258 +/- 0.0014590932777488257</t>
+          <t>-0.0006774361646691207 +/- 0.0023542171960555616</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.005158936946326187 +/- 0.0017509429511632824</t>
+          <t>0.021469515372589888 +/- 0.0012506513809275692</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.003126628452318936 +/- 0.0011883016415832747</t>
+          <t>0.00010422094841061602 +/- 0.0006077073366175414</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.00046899426784781096 +/- 0.0011985409067222644</t>
+          <t>0.002657634184471036 +/- 0.001463738603980006</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0005732152162584492 +/- 0.0004916092304354505</t>
+          <t>-0.0002605523710265678 +/- 0.0002605523710265678</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>0.0003647733194371727 +/- 0.0013598737207607926</t>
+          <t>0.006826472120896265 +/- 0.0013275392603290222</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.0005211047420531911 +/- 0.0014175581561996279</t>
+          <t>-0.00020844189682128755 +/- 0.0011224939670942148</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.00427305888483589 +/- 0.0017251636641216032</t>
+          <t>-0.003126628452318947 +/- 0.0019774534612829824</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0033350703491401346 +/- 0.0012593065110572798</t>
+          <t>0.02209484106305365 +/- 0.0017930849957358314</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>0.00020844189682125424 +/- 0.0004776003850917863</t>
+          <t>0.0013027618551328612 +/- 0.0009955692118052493</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.0007295466388743899 +/- 0.0003456617811730371</t>
+          <t>0.0011464304325168983 +/- 0.000650859614215549</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.005627931214173987 +/- 0.00038995908147722666</t>
+          <t>0.007816571130797256 +/- 0.00046609025065132186</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.009692548202188612 +/- 0.0024904227504634778</t>
+          <t>0.024283480979676884 +/- 0.0015317288646898432</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.0034392912975508396 +/- 0.0018081658752368255</t>
+          <t>-0.0018238665971860746 +/- 0.0016519924423290596</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-0.0010422094841063601 +/- 0.00046609025065135905</t>
+          <t>0.00130276185513285 +/- 0.0005339734635726828</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-0.0023449713392392213 +/- 0.001302761855132879</t>
+          <t>0.0013027618551328724 +/- 0.0018534048195705003</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.0031787389265242605 +/- 0.0024822314463396646</t>
+          <t>-0.00020844189682128755 +/- 0.0016179442101365428</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>-0.0008858780614904082 +/- 0.00023880019254594404</t>
+          <t>0.0022407503908285385 +/- 0.0009336358971948527</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.0007295466388744565 +/- 0.0010474075686421071</t>
+          <t>0.002813965607086999 +/- 0.0013826471246921926</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.003908285565398672 +/- 0.001911112123073714</t>
+          <t>0.0034914017717560864 +/- 0.0022839611256707834</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0.01943720687858257 +/- 0.0008089721050682859</t>
+          <t>0.012714955706096886 +/- 0.0017930849957358335</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-0.00427305888483589 +/- 0.0008965424978679277</t>
+          <t>0.001563314226159429 +/- 0.0006991353759770158</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.00010422094841062712 +/- 0.00020844189682125421</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.0006774361646690874 +/- 0.001142871922848413</t>
+          <t>-0.0004689942678478776 +/- 0.0011523368622978723</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.003751954142782665 +/- 0.0012064447006555692</t>
+          <t>-0.006565919749869742 +/- 0.0007799181629544429</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.0021365294424178782 +/- 0.0007533523863887987</t>
+          <t>0.003074517978113589 +/- 0.0013069240441880537</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-0.005471599791558135 +/- 0.0010742849467476913</t>
+          <t>-0.0010422094841063489 +/- 0.0010422094841063103</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.002084418968212576 +/- 0.00104220948410631</t>
+          <t>0.003022407503908253 +/- 0.0013548723293382006</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-0.00010422094841063822 +/- 0.0005105762882299523</t>
+          <t>-0.00031266284523193686 +/- 0.0019664369217418727</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>-0.00036477331943719494 +/- 0.00023880019254589316</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.00036477331943719494 +/- 0.0005237037843210298</t>
+          <t>0.00010422094841061602 +/- 0.0005612469835471126</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.00020844189682125424 +/- 0.0002552881441149659</t>
+          <t>-0.00036477331943725045 +/- 0.0010171558778501002</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,52 +4826,52 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>-0.0005732152162584824 +/- 0.0005918612137363761</t>
+          <t>0.00020844189682124316 +/- 0.0004776003850918155</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0.00041688379364249737 +/- 0.0008005362947231423</t>
+          <t>-0.0036477331943720937 +/- 0.0011652256266283492</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-5.211047420531356e-05 +/- 0.0001563314226159407</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0013548723293381527 +/- 0.0005802776824210359</t>
+          <t>0.0006774361646690763 +/- 0.0009900990099009984</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>-0.008806670140698325 +/- 0.0013875484060129517</t>
+          <t>-0.00526315789473687 +/- 0.0012646858884327024</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.0012506513809275254 +/- 0.0006673396808163251</t>
+          <t>-0.005523710265763449 +/- 0.0007799181629544369</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>-0.00020844189682126535 +/- 0.00047760038509180573</t>
+          <t>0.0005211047420531356 +/- 0.0005708416440908267</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.0006591511537610097</t>
+          <t>-0.005054715997915604 +/- 0.0010435114327514848</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.002032308494007251 +/- 0.0008222894131349498</t>
+          <t>-0.0002605523710266011 +/- 0.0014223391416317021</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>-0.0007816571130797589 +/- 0.001147614150367131</t>
+          <t>-0.001771756122980772 +/- 0.0007068608632751481</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.004596472474612523 +/- 0.0007633809116561044</t>
+          <t>-0.004703367183324469 +/- 0.0008879341382060829</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,27 +4891,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.003848209513629075 +/- 0.0009797061881252644</t>
+          <t>-0.006253340459647305 +/- 0.0007945520442179803</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.014110101549973286 +/- 0.0016935306806792904</t>
+          <t>-0.014270443613041205 +/- 0.0010154997327632422</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0016568679850347157 +/- 0.00044396706910307355</t>
+          <t>-0.0012292891501871294 +/- 0.0002449265470313243</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.003260288615713536 +/- 0.0008088052351908911</t>
+          <t>-0.0008017103153394323 +/- 0.0008017103153393952</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.0044895777659005875 +/- 0.001269304338539612</t>
+          <t>-0.008123997862105858 +/- 0.0010901164112437885</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4921,62 +4921,62 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.0070550507749866705 +/- 0.0009797061881252306</t>
+          <t>-0.013308391234633921 +/- 0.0015388754728902225</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.0068412613575627775 +/- 0.0012140905068520047</t>
+          <t>0.004970603955104192 +/- 0.0015126639976574033</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.003794762159273113 +/- 0.0009984789787423668</t>
+          <t>0.002672367717797941 +/- 0.0019854810925715393</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.00026723677177977747 +/- 0.0011525311947005947</t>
+          <t>-0.0007482629609834812 +/- 0.0009318864657489425</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.006413682522715136 +/- 0.0011463180432670958</t>
+          <t>-0.010261892036344245 +/- 0.0010635889226152944</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-0.003687867450561222 +/- 0.000939518751001976</t>
+          <t>-0.005558524853019808 +/- 0.0009318864657489528</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.000855157669695339 +/- 0.0016594521321496554</t>
+          <t>-0.004222340994120821 +/- 0.0015573278764653604</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-0.018439337252805988 +/- 0.002320501693863443</t>
+          <t>-0.016568679850347434 +/- 0.002629262186263779</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0019241047568145375 +/- 0.0009620523784072656</t>
+          <t>-0.005505077498663869 +/- 0.0005879208979155665</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.0039016568679850704 +/- 0.0008634684351364785</t>
+          <t>-0.006413682522715158 +/- 0.0012647952502618286</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.0007482629609834257 +/- 0.0007999267529179933</t>
+          <t>-0.0019775521111705663 +/- 0.0008634684351364758</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.013361838588989861 +/- 0.0015490514961185853</t>
+          <t>-0.01608765366114383 +/- 0.001501290422788667</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -4986,62 +4986,62 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00016034206306787536 +/- 0.0014549072783341774</t>
+          <t>0.0017103153393906445 +/- 0.0015079354334223386</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-5.344735435597325e-05 +/- 0.0007726794385249206</t>
+          <t>-0.007803313735970119 +/- 0.0009007108255666957</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-0.001603420630678798 +/- 0.00047804767022975375</t>
+          <t>0.0002137894174237931 +/- 0.0007249951879342768</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>-0.0006413682522715347 +/- 0.0005756456234243302</t>
+          <t>0.00032068412613570627 +/- 0.00026183749254759983</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.0021913415285943483 +/- 0.000734779641093948</t>
+          <t>-0.0018706574024586087 +/- 0.00035853575267230295</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.0009086050240512788 +/- 0.00024492654703127343</t>
+          <t>-0.00010689470871192431 +/- 0.00021378941742384862</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>-0.0013896312132549826 +/- 0.0011758417958311208</t>
+          <t>-0.0010154997327632698 +/- 0.0006070452534260156</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-0.0031533939070016227 +/- 0.0007347796410939301</t>
+          <t>-0.007749866381614146 +/- 0.000933417915370022</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.000748262960983459 +/- 0.0004898530940626292</t>
+          <t>-0.00026723677177982187 +/- 0.0004927602596094616</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.002779262426509899 +/- 0.0007855124776428976</t>
+          <t>-0.004061998931052957 +/- 0.0007633809116560966</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.00016034206306787536 +/- 0.00041743718203669734</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0002137894174237931 +/- 0.0004898530940626001</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.01197220737573491 +/- 0.0017269368702729606</t>
+          <t>-0.01047568145376807 +/- 0.0014181185634870811</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.0058792089791555365 +/- 0.0008280028532779084</t>
+          <t>-0.007963655799037994 +/- 0.0009086050240513153</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5066,107 +5066,107 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.00026723677177981076 +/- 0.0004927602596094797</t>
+          <t>-0.0006413682522715458 +/- 0.00021378941742384862</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.00042757883484769723 +/- 0.0010363826525742995</t>
+          <t>-0.0012827365045430805 +/- 0.000427578834847675</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>-0.0010154997327632364 +/- 0.0010266901503099217</t>
+          <t>-0.0030464991982897204 +/- 0.0007945520442180018</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00047804767022980346</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.00016034206306786425 +/- 0.0006781709000774784</t>
+          <t>5.344735435593995e-05 +/- 0.0002878228117121373</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.0002137894174238153 +/- 0.0006413682522715014</t>
+          <t>-0.0030464991982897317 +/- 0.0006781709000774645</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-0.0002137894174238597 +/- 0.0008348743640733905</t>
+          <t>-0.0009086050240513343 +/- 0.0007577470271917631</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.0006323976251309002</t>
+          <t>0.0005344735435595549 +/- 0.0010953448173126104</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.0011758417958310785 +/- 0.0012140905068519922</t>
+          <t>-0.004168893639764882 +/- 0.0013048162069196898</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.0009620523784072855 +/- 0.0006675572419453063</t>
+          <t>-0.0013361838588990427 +/- 0.0003585357526723278</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.0016568679850347378 +/- 0.0004439670691030441</t>
+          <t>-0.000694815606627508 +/- 0.0003422300501033234</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-5.3447354355962154e-05 +/- 0.00016034206306788645</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0.000908605024051301 +/- 0.0008634684351364785</t>
+          <t>-0.0005344735435596215 +/- 0.00047804767022980346</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>-0.003794762159273146 +/- 0.000652408103459829</t>
+          <t>-0.0034206306787814443 +/- 0.0010473499701905591</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.005077498663816149 +/- 0.0019455130650135053</t>
+          <t>-0.006467129877071121 +/- 0.0018429652217601975</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.01111704970603954 +/- 0.002691539991879033</t>
+          <t>0.005986103687867406 +/- 0.0022140368976170987</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-0.0005344735435596215 +/- 0.0004140014266389757</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.0005879208979155615 +/- 0.0002878228117121373</t>
+          <t>-1.1102230246251566e-17 +/- 0.0002390238351148769</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0032602886157135137 +/- 0.0007726794385248953</t>
+          <t>-0.0005879208979155948 +/- 0.0005042213325524655</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.015606627471940138 +/- 0.003030988108767049</t>
+          <t>-0.0022982362373062948 +/- 0.0017572722846364048</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.000320684126135784 +/- 0.0009620523784072657</t>
+          <t>-0.0006413682522715458 +/- 0.0009195430536656834</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,42 +5176,42 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0.0001068947087119132 +/- 0.0003999633764589936</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-0.0009620523784072965 +/- 0.0005756456234243138</t>
+          <t>-0.0016568679850347823 +/- 0.0007347796410939278</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-0.0019775521111704995 +/- 0.0009869687500063799</t>
+          <t>0.0017103153393906556 +/- 0.0009501009532138417</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>-0.00037413148049173504 +/- 0.0002449265470313243</t>
+          <t>-5.3447354355962154e-05 +/- 0.00016034206306788648</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-0.0003206841261357618 +/- 0.0006413682522715236</t>
+          <t>0.0001068947087119021 +/- 0.0003999633764589818</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.0036344200962052375 +/- 0.0012602700291343256</t>
+          <t>-0.0007482629609834812 +/- 0.0004898530940626194</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.008070550507749852 +/- 0.0012749182727821117</t>
+          <t>-0.0053447354355959705 +/- 0.0013937364842763673</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-0.001603420630678787 +/- 0.0005344735435595771</t>
+          <t>-0.0016034206306788424 +/- 0.00041400142663894704</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-0.00021378941742384862 +/- 0.0005951645497413481</t>
+          <t>0.0006948156066274302 +/- 0.0006346521692697849</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.0014965259219668291 +/- 0.0004659432328744949</t>
+          <t>0.0005344735435595327 +/- 0.00041400142663894704</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.00010689470871192431 +/- 0.0004659432328744949</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-5.3447354355962154e-05 +/- 0.0004439670691030735</t>
+          <t>-0.0005344735435596215 +/- 0.00047804767022980346</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.00080171031533941 +/- 0.0005975595877872245</t>
+          <t>-0.00352752538749338 +/- 0.000354529640871764</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-0.000320684126135784 +/- 0.000595164549741322</t>
+          <t>-0.0008551576696953945 +/- 0.0003545296408717875</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>-0.0006948156066274968 +/- 0.0004174371820366974</t>
+          <t>-0.0009086050240513565 +/- 0.0002449265470313243</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-0.00037413148049173504 +/- 0.00048102618920365937</t>
+          <t>-0.00021378941742387081 +/- 0.0004898530940626146</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>0.00010689470871192431 +/- 0.00021378941742384862</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-0.00021378941742384862 +/- 0.0004275788348476972</t>
+          <t>-0.0029930518439337584 +/- 0.0006413682522715236</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5286,37 +5286,37 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-5.3447354355962154e-05 +/- 0.00016034206306788645</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.0002137894174238597 +/- 0.000684460100206626</t>
+          <t>-0.0007482629609834701 +/- 0.0004275788348476972</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.0011223944414751274 +/- 0.0006948156066274628</t>
+          <t>-0.004115446285408919 +/- 0.0005879208979155383</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>-0.00080171031533941 +/- 0.0004927602596094435</t>
+          <t>0.0002137894174238042 +/- 0.00026183749254759983</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>0.0015499732763228247 +/- 0.0012523115461100997</t>
+          <t>-0.00016034206306789756 +/- 0.000481026189203631</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>-0.0018172100481026355 +/- 0.0005951645497413062</t>
+          <t>-0.0002137894174238597 +/- 0.00035452964087176404</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>-0.0006413682522715458 +/- 0.0003206841261357729</t>
+          <t>-0.0004810261892036705 +/- 0.0005580067615665801</t>
         </is>
       </c>
     </row>
